--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="440">
   <si>
-    <t xml:space="preserve">SSA Commission Tracker — Team Position</t>
+    <t xml:space="preserve">Ampra Commission Tracker — Team Position</t>
   </si>
   <si>
     <t xml:space="preserve">Positions from 20/07/26 onward · HubSpot pull 25/08/26 · ad spend to 20/08/26 · All pending deals are based on cash amounts and may change with finance and ACP charges.</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">READ ME</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA Commission Tracker · pull 25/08/26</t>
+    <t xml:space="preserve">Ampra Commission Tracker · pull 25/08/26</t>
   </si>
   <si>
     <t xml:space="preserve">Who is tracked</t>
@@ -2013,7 +2013,7 @@
         <v>-6370.33</v>
       </c>
       <c r="G5" s="4" t="str">
-        <f aca="false">IF(F5&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(F5&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
       <c r="H5" s="5" t="n">
@@ -2024,8 +2024,8 @@
         <v>2293.97</v>
       </c>
       <c r="J5" s="4" t="str">
-        <f aca="false">IF(I5&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(I5&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2049,7 +2049,7 @@
         <v>-4095.82</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f aca="false">IF(F6&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(F6&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
       <c r="H6" s="5" t="n">
@@ -2060,7 +2060,7 @@
         <v>-824.3</v>
       </c>
       <c r="J6" s="4" t="str">
-        <f aca="false">IF(I6&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(I6&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
     </row>
@@ -2085,8 +2085,8 @@
         <v>686.13</v>
       </c>
       <c r="G7" s="4" t="str">
-        <f aca="false">IF(F7&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(F7&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>11804.4</v>
@@ -2096,8 +2096,8 @@
         <v>12490.53</v>
       </c>
       <c r="J7" s="4" t="str">
-        <f aca="false">IF(I7&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(I7&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2121,7 +2121,7 @@
         <v>-3300.01</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f aca="false">IF(F8&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(F8&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
       <c r="H8" s="5" t="n">
@@ -2132,7 +2132,7 @@
         <v>-960.37</v>
       </c>
       <c r="J8" s="4" t="str">
-        <f aca="false">IF(I8&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(I8&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
     </row>
@@ -2157,8 +2157,8 @@
         <v>0</v>
       </c>
       <c r="G9" s="4" t="str">
-        <f aca="false">IF(F9&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(F9&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>615.7</v>
@@ -2168,8 +2168,8 @@
         <v>615.7</v>
       </c>
       <c r="J9" s="4" t="str">
-        <f aca="false">IF(I9&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(I9&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2196,7 +2196,7 @@
         <v>-13080.03</v>
       </c>
       <c r="G10" s="7" t="str">
-        <f aca="false">IF(F10&gt;=0,"SSA OWES","TO EARN BACK")</f>
+        <f aca="false">IF(F10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
         <v>TO EARN BACK</v>
       </c>
       <c r="H10" s="8" t="n">
@@ -2208,8 +2208,8 @@
         <v>13615.53</v>
       </c>
       <c r="J10" s="7" t="str">
-        <f aca="false">IF(I10&gt;=0,"SSA OWES","TO EARN BACK")</f>
-        <v>SSA OWES</v>
+        <f aca="false">IF(I10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
+        <v>AMPRA OWES</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -74,10 +74,10 @@
     <t xml:space="preserve">Joe</t>
   </si>
   <si>
+    <t xml:space="preserve">Holly</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holly</t>
   </si>
   <si>
     <t xml:space="preserve">Ollie</t>
@@ -2069,7 +2069,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>35</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>15</v>
@@ -3240,7 +3240,7 @@
         <v>139</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>140</v>
@@ -3260,7 +3260,7 @@
         <v>142</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>140</v>
@@ -3280,7 +3280,7 @@
         <v>143</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>140</v>
@@ -3320,7 +3320,7 @@
         <v>144</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>145</v>
@@ -3340,7 +3340,7 @@
         <v>147</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>140</v>
@@ -3360,7 +3360,7 @@
         <v>147</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>140</v>
@@ -3380,7 +3380,7 @@
         <v>150</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>140</v>
@@ -3400,7 +3400,7 @@
         <v>151</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>140</v>
@@ -3420,7 +3420,7 @@
         <v>152</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>140</v>
@@ -3440,7 +3440,7 @@
         <v>153</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>140</v>
@@ -3460,7 +3460,7 @@
         <v>154</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>140</v>
@@ -3480,7 +3480,7 @@
         <v>155</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>140</v>
@@ -3520,7 +3520,7 @@
         <v>156</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>145</v>
@@ -3540,7 +3540,7 @@
         <v>156</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>140</v>
@@ -3560,7 +3560,7 @@
         <v>157</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>140</v>
@@ -3580,7 +3580,7 @@
         <v>158</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>140</v>
@@ -3600,7 +3600,7 @@
         <v>159</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>140</v>
@@ -3620,7 +3620,7 @@
         <v>160</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>140</v>
@@ -3640,7 +3640,7 @@
         <v>161</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>140</v>
@@ -3660,7 +3660,7 @@
         <v>162</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>140</v>
@@ -3680,7 +3680,7 @@
         <v>163</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>140</v>
@@ -3928,7 +3928,7 @@
         <v>183</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>14</v>
@@ -4090,7 +4090,7 @@
         <v>208</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>15</v>
@@ -4117,7 +4117,7 @@
         <v>211</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>212</v>
@@ -5311,7 +5311,7 @@
         <v>352</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>15</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>427</v>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="469">
   <si>
     <t xml:space="preserve">Ampra Commission Tracker — Team Position</t>
   </si>
@@ -525,12 +525,18 @@
     <t xml:space="preserve">Reconciliation - confirmed commission vs estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Cycle 26/08/26 · installed deals from 20/07/26 with all Xero figures confirmed · 7 reconciled, 4 not ready to pay</t>
+    <t xml:space="preserve">Cycle 26/08/26 · every installed deal with all Xero figures confirmed · 73 reconciled, 6 not ready to pay</t>
   </si>
   <si>
     <t xml:space="preserve">Net Revenue = Xero Revenue + ACP (Formbay) impact + Finance Fee impact, and is already GST-exclusive - it is never divided by 1.1. Commission Payable = 10% of Net Revenue, computed here rather than read from HubSpot: as at 26/08/26 the HubSpot field subtracts the ACP impact where Net Revenue adds it, so it is wrong on every deal with an ACP adjustment. Scott is correcting it at source. The pot is then split by the ordinary rules - Away by headcount, Home half to lead gen and half to specialist.</t>
   </si>
   <si>
+    <t xml:space="preserve">Deals installed before 20/07/26 are locked in for the historical record only. They do NOT affect current positions - the tracker still counts commission forward from 20/07/26 and reopening that baseline is not intended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Era</t>
+  </si>
+  <si>
     <t xml:space="preserve">Installed</t>
   </si>
   <si>
@@ -558,18 +564,18 @@
     <t xml:space="preserve">Variance</t>
   </si>
   <si>
+    <t xml:space="preserve">180526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christine &amp; Peter Broderick - 24 Frazer Street Ashford NSW 2361</t>
+  </si>
+  <si>
     <t xml:space="preserve">190626.DWB01</t>
   </si>
   <si>
     <t xml:space="preserve">Katie Young - 66 Dangar Street Narrabri NSW 2390</t>
   </si>
   <si>
-    <t xml:space="preserve">180526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christine &amp; Peter Broderick - 24 Frazer Street Ashford NSW 2361</t>
-  </si>
-  <si>
     <t xml:space="preserve">190626.DWB03</t>
   </si>
   <si>
@@ -606,18 +612,585 @@
     <t xml:space="preserve">25/07/26</t>
   </si>
   <si>
+    <t xml:space="preserve">Historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Fitz - 46 Churchill Avenue Orange NSW 2800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/10/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Hart - 46 Grimshaw Street Richardson ACT 2905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/10/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Middleton - 35 Cooya Beach Road Bonnie Doon QLD 4873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/11/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Satrapa -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/11/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Olley - 7 Dixon Place Jerrabomberra NSW 2619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/12/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor Haskins - 77 Lambeth Street Glen Innes NSW 2370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/12/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cecilia Curtis - 10 Sinclair Street Kambah ACT 2902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/12/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judy Mannix - 68 Clanwilliam Street Blackheath NSW 2785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Scofield &amp; Liz Mitchelson - 7674 Bruxner Highway Drake NSW 2469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/01/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dale Baldock - 85 Finch Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/01/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandra de Jong - 9 White Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glenda Eyears - 4 Wood Street Tenterfield NSW 2372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/01/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Schriever - 32 Bungama Street Maroochydore QLD 4558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/01/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tony Tedesco - 7 Wasley Road Wasleys SA 5400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larry Grant - 77 Cecil Road Orange NSW 2800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Watt - 41 Milburn Place St Ives Chase NSW 2075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Cummins - 9 Waipori Street St Ives Chase NSW 2075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Rallings - 122 Eyles Drive East Ballina NSW 2478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria E Kelly - 2529 Pyramids Road Wyberba QLD 4382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Bob &amp; Lawson Muir - 1787 Delubngra Road Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Bob &amp; Lawson Muir - 1516 Delungra Road Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Heath - Unit 5 - 11 Prospect Street Mackay QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marion Priestly - 31 Adams Street Heddon Greta NSW 2321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Campbell - 11 Vesta Lane Ooralea QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Schaper - 22 Elizabeth Street Mirani QLD 4754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vincent Reeves - 5 Lucy Court Mirani QLD 4754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernie Shields - 9 Coral Drive Blacks Beach QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Boland - 16 Blackmur Street Marian QLD 4753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gibb French - 34 Alan Street Marian QLD 4753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Tooler - 8 Tranquil Place Alstonville NSW 2477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Mooney - 17 Philip Street South Golden Beach NSW 2483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andy Callaway - 69 Maitland Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Dick - 36 Keera Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dianne Burke - 91 Cunningham Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annette Towers - 2 Finch Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Moore - 93 Stephen Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosemary Arnold - 38 Holden Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Campbell - 100 Dunwold-Cattle Creek Road Gargett QLD 4741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rob Matta - 109 Brighton Street Croydon Park NSW 2133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen Paskins - 11 Heathwood Court Hampden QLD 4741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy Wong - 10 O'Connor Street Eastlakes NSW 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210426.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serena Kash - 23 Crane Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260426.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Hancock - 105 High Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040526.DWB03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Gray - 10 Cross Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230426.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felicity Menchin - 28 Inverell Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer Stewart - 3-5 Gleno Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicki Davis - 36 Burnett Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Woodmansey - 126-128 Hoddle Street Howlong NSW 2643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180526.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dee &amp; Steve Mansfield - 6 Rosewood Place Kyogle NSW 2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Jolly - 11 Ness Street Diamond Creek VIC 3089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allan Marks - 27 Hay Road Cable Beach WA 6726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mick Prokopiwskyi - 9 McMillan Court Newborough VIC 3825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ian Mcgrath - 6 Rivergum Avenue Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don Wood - 11 Pembroke Road Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160526.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christopher Hutton - 31 Boorabee Street Kyogle NSW 2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Currell - 37 Cameron Street Maclean NSW 2463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100626.JS02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee Achurch - 11 Myall Street Evans Head NSW 2473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosalee &amp; Greg Foran - 2 Bank Street Woodburn NSW 2471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130526.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daryl Boyd - 48 Martyn Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Moore - 6 Bank Street Woodburn NSW 2472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190526.DWB04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverly &amp; Graeme Voss - 3 David Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Craig Robinson- 14 Cedar Street Woodburn NSW 2472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry O'Farrell - 45 Frazer Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100626.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgina Kelly - 21 Puertollano Place Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristopher Iquin - 5 Euro Way Djugun WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120626.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebecca Hudson - 93 Main Street Clunes NSW 2480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/26</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOT READY TO PAY</t>
   </si>
   <si>
+    <t xml:space="preserve">Dee &amp; Steve Mansfield - 206 Summerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">figures incomplete - not ready to pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer Stewart 1 Gleno</t>
+  </si>
+  <si>
     <t xml:space="preserve">150626.DWB01</t>
   </si>
   <si>
     <t xml:space="preserve">Mark Wilson</t>
   </si>
   <si>
-    <t xml:space="preserve">figures incomplete - not ready to pay</t>
-  </si>
-  <si>
     <t xml:space="preserve">130726.JS01</t>
   </si>
   <si>
@@ -702,649 +1275,91 @@
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Dermot; Rosa</t>
   </si>
   <si>
-    <t xml:space="preserve">120626.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebecca Hudson - 93 Main Street Clunes NSW 2480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cian Jefferson; Hugo</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristopher Iquin - 5 Euro Way Djugun WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100626.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgina Kelly - 21 Puertollano Place Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cian Jefferson</t>
   </si>
   <si>
-    <t xml:space="preserve">230526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barry O'Farrell - 45 Frazer Street Ashford NSW 2361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Hugo; Max Bradfield; Rosa; Dermot; Fran</t>
   </si>
   <si>
-    <t xml:space="preserve">Craig Robinson- 14 Cedar Street Woodburn NSW 2472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Harley</t>
   </si>
   <si>
-    <t xml:space="preserve">190526.DWB04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverly &amp; Graeme Voss - 3 David Street Ashford NSW 2361</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rosa; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran</t>
   </si>
   <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Rosa; Dermot</t>
   </si>
   <si>
-    <t xml:space="preserve">070426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Moore - 6 Bank Street Woodburn NSW 2472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fran</t>
   </si>
   <si>
-    <t xml:space="preserve">130526.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daryl Boyd - 48 Martyn Street Ashford NSW 2361</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Mark Isaac; Joe</t>
   </si>
   <si>
     <t xml:space="preserve">Cian Jefferson; Denzel Winterbeard; Max Bradfield; Hugo; Mark Isaac; Joe</t>
   </si>
   <si>
-    <t xml:space="preserve">070526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosalee &amp; Greg Foran - 2 Bank Street Woodburn NSW 2471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100626.JS02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee Achurch - 11 Myall Street Evans Head NSW 2473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrian Currell - 37 Cameron Street Maclean NSW 2463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160526.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christopher Hutton - 31 Boorabee Street Kyogle NSW 2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don Wood - 11 Pembroke Road Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ian Mcgrath - 6 Rivergum Avenue Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mick Prokopiwskyi - 9 McMillan Court Newborough VIC 3825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allan Marks - 27 Hay Road Cable Beach WA 6726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Jolly - 11 Ness Street Diamond Creek VIC 3089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180526.JS01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dee &amp; Steve Mansfield - 206 Summerland Way Kyogle NSW 2474</t>
   </si>
   <si>
-    <t xml:space="preserve">03/06/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joe; Dermot</t>
   </si>
   <si>
     <t xml:space="preserve">no deal value</t>
   </si>
   <si>
-    <t xml:space="preserve">Dee &amp; Steve Mansfield - 6 Rosewood Place Kyogle NSW 2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">no attribution</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Woodmansey - 126-128 Hoddle Street Howlong NSW 2643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250426.DWB01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Summer Stewart - 1 Gleno Street Delungra NSW 2403</t>
   </si>
   <si>
-    <t xml:space="preserve">23/05/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cian Jefferson; Max Bradfield; Hugo; Denzel Winterbeard; Mark Isaac</t>
   </si>
   <si>
-    <t xml:space="preserve">230426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicki Davis - 36 Burnett Street Delungra NSW 2403</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hugo; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Mark Isaac</t>
   </si>
   <si>
-    <t xml:space="preserve">Summer Stewart - 3-5 Gleno Street Delungra NSW 2403</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cian Jefferson; Hugo; Max Bradfield; Mark Isaac; Denzel Winterbeard</t>
   </si>
   <si>
-    <t xml:space="preserve">230426.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felicity Menchin - 28 Inverell Street Delungra NSW 2403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/05/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Max Bradfield; Hugo; Cian Jefferson; Mark Isaac</t>
   </si>
   <si>
-    <t xml:space="preserve">040526.DWB03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Gray - 10 Cross Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/05/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hugo; Max Bradfield; Cian Jefferson; Mark Isaac; Denzel Winterbeard</t>
   </si>
   <si>
-    <t xml:space="preserve">260426.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Hancock - 105 High Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210426.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serena Kash - 23 Crane Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Mark Isaac; Hugo</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amy Wong - 10 O'Connor Street Eastlakes NSW 2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rob Matta - 109 Brighton Street Croydon Park NSW 2133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allen Paskins - 11 Heathwood Court Hampden QLD 4741</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joe; Denzel Winterbeard; Cian Jefferson; Fran; Max Bradfield</t>
   </si>
   <si>
     <t xml:space="preserve">Joe; Simon; Denzel Winterbeard; Cian Jefferson; Max Bradfield</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Campbell - 100 Dunwold-Cattle Creek Road Gargett QLD 4741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosemary Arnold - 38 Holden Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/04/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Harley; Max Bradfield; Cian Jefferson</t>
   </si>
   <si>
     <t xml:space="preserve">Denzel Winterbeard; Max Bradfield; Harley; Cian Jefferson</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Moore - 93 Stephen Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dianne Burke - 91 Cunningham Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Max Bradfield; Cian Jefferson; Hugo</t>
   </si>
   <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annette Towers - 2 Finch Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andy Callaway - 69 Maitland Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrian Dick - 36 Keera Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Mooney - 17 Philip Street South Golden Beach NSW 2483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Tooler - 8 Tranquil Place Alstonville NSW 2477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gibb French - 34 Alan Street Marian QLD 4753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bernie Shields - 9 Coral Drive Blacks Beach QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Boland - 16 Blackmur Street Marian QLD 4753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vincent Reeves - 5 Lucy Court Mirani QLD 4754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Schaper - 22 Elizabeth Street Mirani QLD 4754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Campbell - 11 Vesta Lane Ooralea QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/04/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dermot</t>
   </si>
   <si>
-    <t xml:space="preserve">SSA018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marion Priestly - 31 Adams Street Heddon Greta NSW 2321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Heath - Unit 5 - 11 Prospect Street Mackay QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Bob &amp; Lawson Muir - 1516 Delungra Road Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Bob &amp; Lawson Muir - 1787 Delubngra Road Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria E Kelly - 2529 Pyramids Road Wyberba QLD 4382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/03/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Joe</t>
   </si>
   <si>
     <t xml:space="preserve">Joe; Denzel Winterbeard; Cian Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Rallings - 122 Eyles Drive East Ballina NSW 2478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Cummins - 9 Waipori Street St Ives Chase NSW 2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Watt - 41 Milburn Place St Ives Chase NSW 2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larry Grant - 77 Cecil Road Orange NSW 2800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tony Tedesco - 7 Wasley Road Wasleys SA 5400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Schriever - 32 Bungama Street Maroochydore QLD 4558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/01/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glenda Eyears - 4 Wood Street Tenterfield NSW 2372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/01/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandra de Jong - 9 White Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/01/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dale Baldock - 85 Finch Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Scofield &amp; Liz Mitchelson - 7674 Bruxner Highway Drake NSW 2469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/01/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cecilia Curtis - 10 Sinclair Street Kambah ACT 2902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/12/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judy Mannix - 68 Clanwilliam Street Blackheath NSW 2785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor Haskins - 77 Lambeth Street Glen Innes NSW 2370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/12/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Olley - 7 Dixon Place Jerrabomberra NSW 2619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/12/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Satrapa -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/11/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Middleton - 35 Cooya Beach Road Bonnie Doon QLD 4873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/11/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Hart - 46 Grimshaw Street Richardson ACT 2905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/10/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Fitz - 46 Churchill Avenue Orange NSW 2800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/10/25</t>
   </si>
   <si>
     <t xml:space="preserve">READ ME</t>
@@ -1616,7 +1631,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1717,7 +1732,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1725,7 +1740,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3825,17 +3844,18 @@
     <tabColor rgb="FFFFC700"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,6 +3872,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -3867,6 +3888,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
@@ -3883,423 +3905,3023 @@
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="K6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E7" s="6" t="n">
+        <v>6876.36</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-416</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>6460.36</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>646.04</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>182.64</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>184.58</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>31083.64</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>525.09</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-4923.32</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>26685.41</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>2668.54</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>1052.54</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>1067.42</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>14.88</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>6876.36</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>-416</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>6460.36</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>646.04</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>182.64</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>184.58</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>17942.73</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>161.82</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>18104.55</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>1810.45</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>717.7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>724.18</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>6.48</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>25673.64</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>613.45</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>-4240.42</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>22046.67</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>2204.67</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>864.1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>881.86</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>17.76</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="C11" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>61751.82</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>627.64</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>62379.46</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>6237.95</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>2058.39</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>2079.33</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>20.94</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>17942.73</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>18075.73</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>1807.57</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>1404.38</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>1807.56</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L12" s="6" t="n">
         <v>403.18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="C13" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>32140.91</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>-355.5</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>-5082.18</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H13" s="6" t="n">
         <v>26703.23</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>2670.32</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>1285.64</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>1068.12</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="L13" s="6" t="n">
         <v>-217.52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8" t="n">
-        <f aca="false">SUM(D6:D12)</f>
-        <v>193411.83</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <f aca="false">SUM(E6:E12)</f>
-        <v>1289.5</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <f aca="false">SUM(F6:F12)</f>
-        <v>-14245.92</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <f aca="false">SUM(G6:G12)</f>
-        <v>180455.41</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <f aca="false">SUM(H6:H12)</f>
-        <v>18045.54</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <f aca="false">SUM(I6:I12)</f>
-        <v>7565.39</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <f aca="false">SUM(J6:J12)</f>
-        <v>7813.05</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <f aca="false">SUM(K6:K12)</f>
-        <v>247.66</v>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>4086.36</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>4086.36</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>408.64</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>500</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>408.64</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <v>-91.36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>2722.73</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>2722.73</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>272.27</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>454.55</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>272.27</v>
+      </c>
+      <c r="L15" s="27" t="n">
+        <v>-182.28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>17727.27</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>17727.27</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>1772.73</v>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>1818.18</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>1772.73</v>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>-45.45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>136.36</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>136.36</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>9995</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>9995</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>999.5</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>909.09</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>999.5</v>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>90.41</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>5250</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>525</v>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>477.27</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>525</v>
+      </c>
+      <c r="L19" s="27" t="n">
+        <v>47.73</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>3631.82</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>3631.82</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>363.18</v>
+      </c>
+      <c r="J20" s="27" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>181.59</v>
+      </c>
+      <c r="L20" s="27" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>2722.73</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>2722.73</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>272.27</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>454.55</v>
+      </c>
+      <c r="K21" s="27" t="n">
+        <v>272.27</v>
+      </c>
+      <c r="L21" s="27" t="n">
+        <v>-182.28</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>15984.55</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>-81.82</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>15902.73</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>1590.27</v>
+      </c>
+      <c r="J22" s="27" t="n">
+        <v>1065.64</v>
+      </c>
+      <c r="K22" s="27" t="n">
+        <v>1060.18</v>
+      </c>
+      <c r="L22" s="27" t="n">
+        <v>-5.46</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>12297.82</v>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>171.27</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>12469.09</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>1246.91</v>
+      </c>
+      <c r="J23" s="27" t="n">
+        <v>1229.78</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>1246.91</v>
+      </c>
+      <c r="L23" s="27" t="n">
+        <v>17.13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>9753.64</v>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>-81.82</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>9671.82</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>967.18</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>975.36</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>967.18</v>
+      </c>
+      <c r="L24" s="27" t="n">
+        <v>-8.18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>20173.64</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>-122.73</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>20050.91</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>2005.09</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <v>1345.52</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>1336.72</v>
+      </c>
+      <c r="L25" s="27" t="n">
+        <v>-8.8</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>14123.27</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>14478.36</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>1447.84</v>
+      </c>
+      <c r="J26" s="27" t="n">
+        <v>1412.33</v>
+      </c>
+      <c r="K26" s="27" t="n">
+        <v>1447.84</v>
+      </c>
+      <c r="L26" s="27" t="n">
+        <v>35.51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>7673.64</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>7673.64</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>767.36</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>5250</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>525</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="L28" s="27" t="n">
+        <v>35.23</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>14318.18</v>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>-647.27</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>13670.91</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>1367.09</v>
+      </c>
+      <c r="J29" s="27" t="n">
+        <v>1383.45</v>
+      </c>
+      <c r="K29" s="27" t="n">
+        <v>1367.09</v>
+      </c>
+      <c r="L29" s="27" t="n">
+        <v>-16.36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="27" t="n">
+        <v>19359.09</v>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>1400.45</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>20759.54</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>2075.95</v>
+      </c>
+      <c r="J30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>11706.91</v>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>171.27</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>11878.18</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>1187.82</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>585.35</v>
+      </c>
+      <c r="K31" s="27" t="n">
+        <v>593.91</v>
+      </c>
+      <c r="L31" s="27" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>26745.64</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>336.09</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>27081.73</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>2708.17</v>
+      </c>
+      <c r="J32" s="27" t="n">
+        <v>1783.04</v>
+      </c>
+      <c r="K32" s="27" t="n">
+        <v>1805.44</v>
+      </c>
+      <c r="L32" s="27" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>33123.82</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>3526</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>-4925.66</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>31724.16</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>3172.42</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>3312.38</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>3172.42</v>
+      </c>
+      <c r="L33" s="27" t="n">
+        <v>-139.96</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>55068.18</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>3168.36</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>-8450.15</v>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>49786.39</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>4978.64</v>
+      </c>
+      <c r="J34" s="27" t="n">
+        <v>5219.02</v>
+      </c>
+      <c r="K34" s="27" t="n">
+        <v>4978.64</v>
+      </c>
+      <c r="L34" s="27" t="n">
+        <v>-240.38</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="E35" s="27" t="n">
+        <v>17844.55</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>17344.55</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>1734.45</v>
+      </c>
+      <c r="J35" s="27" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="K35" s="27" t="n">
+        <v>1734.46</v>
+      </c>
+      <c r="L35" s="27" t="n">
+        <v>616.36</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>17268.18</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>-636.36</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>16631.82</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>1663.18</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <v>20250</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>-5207.27</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>15042.73</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>22776.37</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>2040.91</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>-3227.41</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>21589.87</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>2158.99</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>2717.27</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>2158.99</v>
+      </c>
+      <c r="L38" s="27" t="n">
+        <v>-558.28</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <v>24076.18</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>-899.82</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>-2369.25</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>20807.11</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>2080.71</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <v>821.18</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <v>693.58</v>
+      </c>
+      <c r="L39" s="27" t="n">
+        <v>-127.6</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E40" s="27" t="n">
+        <v>30136.37</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>-3362.18</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>-3499.06</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>23275.13</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>2327.51</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>921.04</v>
+      </c>
+      <c r="K40" s="27" t="n">
+        <v>775.84</v>
+      </c>
+      <c r="L40" s="27" t="n">
+        <v>-145.2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <v>28526.55</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>-1460.73</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>-3466.88</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>23598.94</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>2359.89</v>
+      </c>
+      <c r="J41" s="27" t="n">
+        <v>912.54</v>
+      </c>
+      <c r="K41" s="27" t="n">
+        <v>786.62</v>
+      </c>
+      <c r="L41" s="27" t="n">
+        <v>-125.92</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" s="27" t="n">
+        <v>43775.27</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>-375.09</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>-6316.29</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>37083.89</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>3708.39</v>
+      </c>
+      <c r="J42" s="27" t="n">
+        <v>1459.18</v>
+      </c>
+      <c r="K42" s="27" t="n">
+        <v>1236.12</v>
+      </c>
+      <c r="L42" s="27" t="n">
+        <v>-223.06</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>28636.36</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>-704.72</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>27931.64</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>2793.16</v>
+      </c>
+      <c r="J43" s="27" t="n">
+        <v>2822.65</v>
+      </c>
+      <c r="K43" s="27" t="n">
+        <v>2793.16</v>
+      </c>
+      <c r="L43" s="27" t="n">
+        <v>-29.49</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>65188.18</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>1646.82</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>66835</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>6683.5</v>
+      </c>
+      <c r="J44" s="27" t="n">
+        <v>3270.6</v>
+      </c>
+      <c r="K44" s="27" t="n">
+        <v>3341.75</v>
+      </c>
+      <c r="L44" s="27" t="n">
+        <v>71.15</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <v>30709.09</v>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>71.82</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>30780.91</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>3078.09</v>
+      </c>
+      <c r="J45" s="27" t="n">
+        <v>729.49</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>769.52</v>
+      </c>
+      <c r="L45" s="27" t="n">
+        <v>40.03</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E46" s="27" t="n">
+        <v>13304.54</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>1120.37</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>14424.91</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>1442.49</v>
+      </c>
+      <c r="J46" s="27" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="K46" s="27" t="n">
+        <v>360.62</v>
+      </c>
+      <c r="L46" s="27" t="n">
+        <v>23.09</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" s="27" t="n">
+        <v>21751.81</v>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>-761.36</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>20990.45</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>2099.05</v>
+      </c>
+      <c r="J47" s="27" t="n">
+        <v>1102.28</v>
+      </c>
+      <c r="K47" s="27" t="n">
+        <v>1049.52</v>
+      </c>
+      <c r="L47" s="27" t="n">
+        <v>-52.76</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>37204.55</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>-3412.73</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>-3424.52</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>30367.3</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>3036.73</v>
+      </c>
+      <c r="J48" s="27" t="n">
+        <v>880.64</v>
+      </c>
+      <c r="K48" s="27" t="n">
+        <v>759.18</v>
+      </c>
+      <c r="L48" s="27" t="n">
+        <v>-121.46</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E49" s="27" t="n">
+        <v>26544.73</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>-610</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>25934.73</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>2593.47</v>
+      </c>
+      <c r="J49" s="27" t="n">
+        <v>663.62</v>
+      </c>
+      <c r="K49" s="27" t="n">
+        <v>648.37</v>
+      </c>
+      <c r="L49" s="27" t="n">
+        <v>-15.25</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <v>20408.18</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>993.64</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>-1446.52</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>19955.3</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>1995.53</v>
+      </c>
+      <c r="J50" s="27" t="n">
+        <v>534.7</v>
+      </c>
+      <c r="K50" s="27" t="n">
+        <v>498.88</v>
+      </c>
+      <c r="L50" s="27" t="n">
+        <v>-35.82</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>52279.51</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>-5689.37</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>46590.14</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>4659.01</v>
+      </c>
+      <c r="J51" s="27" t="n">
+        <v>4858.92</v>
+      </c>
+      <c r="K51" s="27" t="n">
+        <v>4659.01</v>
+      </c>
+      <c r="L51" s="27" t="n">
+        <v>-199.91</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>25545.45</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>-4801.09</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>20744.36</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>2074.44</v>
+      </c>
+      <c r="J52" s="27" t="n">
+        <v>1228.43</v>
+      </c>
+      <c r="K52" s="27" t="n">
+        <v>1037.22</v>
+      </c>
+      <c r="L52" s="27" t="n">
+        <v>-191.21</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>25261</v>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>1548.55</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>26809.55</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>2680.95</v>
+      </c>
+      <c r="J53" s="27" t="n">
+        <v>583.68</v>
+      </c>
+      <c r="K53" s="27" t="n">
+        <v>893.64</v>
+      </c>
+      <c r="L53" s="27" t="n">
+        <v>309.96</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>27253.63</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>455.09</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>27708.72</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>2770.87</v>
+      </c>
+      <c r="J54" s="27" t="n">
+        <v>3069.24</v>
+      </c>
+      <c r="K54" s="27" t="n">
+        <v>2770.87</v>
+      </c>
+      <c r="L54" s="27" t="n">
+        <v>-298.37</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="E55" s="27" t="n">
+        <v>30827.27</v>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>566</v>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="27" t="n">
+        <v>31393.27</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>3139.33</v>
+      </c>
+      <c r="J55" s="27" t="n">
+        <v>1312.22</v>
+      </c>
+      <c r="K55" s="27" t="n">
+        <v>1255.74</v>
+      </c>
+      <c r="L55" s="27" t="n">
+        <v>-56.48</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <v>20118.18</v>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>1077.09</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>21195.27</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>2119.53</v>
+      </c>
+      <c r="J56" s="27" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="K56" s="27" t="n">
+        <v>847.82</v>
+      </c>
+      <c r="L56" s="27" t="n">
+        <v>24.92</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="E57" s="27" t="n">
+        <v>22090</v>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>-138.91</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="27" t="n">
+        <v>21951.09</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>2195.11</v>
+      </c>
+      <c r="J57" s="27" t="n">
+        <v>896.98</v>
+      </c>
+      <c r="K57" s="27" t="n">
+        <v>878.04</v>
+      </c>
+      <c r="L57" s="27" t="n">
+        <v>-18.94</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="E58" s="27" t="n">
+        <v>33354.55</v>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>-949.8</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>-5225.2</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>27179.55</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>2717.95</v>
+      </c>
+      <c r="J58" s="27" t="n">
+        <v>1292.66</v>
+      </c>
+      <c r="K58" s="27" t="n">
+        <v>1087.18</v>
+      </c>
+      <c r="L58" s="27" t="n">
+        <v>-205.48</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>34665.68</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>-5624.98</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>29040.7</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>2904.07</v>
+      </c>
+      <c r="J59" s="27" t="n">
+        <v>1137</v>
+      </c>
+      <c r="K59" s="27" t="n">
+        <v>1161.62</v>
+      </c>
+      <c r="L59" s="27" t="n">
+        <v>24.62</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>21516.36</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>-3148.25</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>18368.11</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>1836.81</v>
+      </c>
+      <c r="J60" s="27" t="n">
+        <v>824.3</v>
+      </c>
+      <c r="K60" s="27" t="n">
+        <v>734.72</v>
+      </c>
+      <c r="L60" s="27" t="n">
+        <v>-89.58</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>-2419.64</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>-1920.55</v>
+      </c>
+      <c r="H61" s="27" t="n">
+        <v>15159.81</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>1515.98</v>
+      </c>
+      <c r="J61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62" s="27" t="n">
+        <v>41930</v>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>1210.09</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="27" t="n">
+        <v>43140.09</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>4314.01</v>
+      </c>
+      <c r="J62" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>25390</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>204.37</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="27" t="n">
+        <v>25594.37</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="27" t="n">
+        <v>1622.67</v>
+      </c>
+      <c r="K63" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="27" t="n">
+        <v>-1622.67</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <v>21468.18</v>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>-49.27</v>
+      </c>
+      <c r="G64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="27" t="n">
+        <v>21418.91</v>
+      </c>
+      <c r="I64" s="27" t="n">
+        <v>2141.89</v>
+      </c>
+      <c r="J64" s="27" t="n">
+        <v>2364.69</v>
+      </c>
+      <c r="K64" s="27" t="n">
+        <v>2141.89</v>
+      </c>
+      <c r="L64" s="27" t="n">
+        <v>-222.8</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>31957.27</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>-1183.27</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="27" t="n">
+        <v>30774</v>
+      </c>
+      <c r="I65" s="27" t="n">
+        <v>3077.4</v>
+      </c>
+      <c r="J65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="E66" s="27" t="n">
+        <v>44461.82</v>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>989.09</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>-6987.26</v>
+      </c>
+      <c r="H66" s="27" t="n">
+        <v>38463.65</v>
+      </c>
+      <c r="I66" s="27" t="n">
+        <v>3846.37</v>
+      </c>
+      <c r="J66" s="27" t="n">
+        <v>4128.8</v>
+      </c>
+      <c r="K66" s="27" t="n">
+        <v>3846.37</v>
+      </c>
+      <c r="L66" s="27" t="n">
+        <v>-282.43</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="E67" s="27" t="n">
+        <v>63424.55</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>1616</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>-9847.73</v>
+      </c>
+      <c r="H67" s="27" t="n">
+        <v>55192.82</v>
+      </c>
+      <c r="I67" s="27" t="n">
+        <v>5519.28</v>
+      </c>
+      <c r="J67" s="27" t="n">
+        <v>7168</v>
+      </c>
+      <c r="K67" s="27" t="n">
+        <v>5519.28</v>
+      </c>
+      <c r="L67" s="27" t="n">
+        <v>-1648.72</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="E68" s="27" t="n">
+        <v>18519.3</v>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>-19.27</v>
+      </c>
+      <c r="G68" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="27" t="n">
+        <v>18500.03</v>
+      </c>
+      <c r="I68" s="27" t="n">
+        <v>1850</v>
+      </c>
+      <c r="J68" s="27" t="n">
+        <v>935.7</v>
+      </c>
+      <c r="K68" s="27" t="n">
+        <v>1233.34</v>
+      </c>
+      <c r="L68" s="27" t="n">
+        <v>297.64</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D69" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="E69" s="27" t="n">
+        <v>14989.09</v>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="G69" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="27" t="n">
+        <v>15012.36</v>
+      </c>
+      <c r="I69" s="27" t="n">
+        <v>1501.24</v>
+      </c>
+      <c r="J69" s="27" t="n">
+        <v>1498.9</v>
+      </c>
+      <c r="K69" s="27" t="n">
+        <v>1501.24</v>
+      </c>
+      <c r="L69" s="27" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="E70" s="27" t="n">
+        <v>11750</v>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>-40.23</v>
+      </c>
+      <c r="G70" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="27" t="n">
+        <v>11709.77</v>
+      </c>
+      <c r="I70" s="27" t="n">
+        <v>1170.98</v>
+      </c>
+      <c r="J70" s="27" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="K70" s="27" t="n">
+        <v>585.49</v>
+      </c>
+      <c r="L70" s="27" t="n">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="D71" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="E71" s="27" t="n">
+        <v>27150</v>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>188.36</v>
+      </c>
+      <c r="G71" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="27" t="n">
+        <v>27338.36</v>
+      </c>
+      <c r="I71" s="27" t="n">
+        <v>2733.84</v>
+      </c>
+      <c r="J71" s="27" t="n">
+        <v>1073.41</v>
+      </c>
+      <c r="K71" s="27" t="n">
+        <v>1366.92</v>
+      </c>
+      <c r="L71" s="27" t="n">
+        <v>293.51</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="E72" s="27" t="n">
+        <v>22616.36</v>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>-265.09</v>
+      </c>
+      <c r="G72" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="27" t="n">
+        <v>22351.27</v>
+      </c>
+      <c r="I72" s="27" t="n">
+        <v>2235.13</v>
+      </c>
+      <c r="J72" s="27" t="n">
+        <v>1130.82</v>
+      </c>
+      <c r="K72" s="27" t="n">
+        <v>1117.56</v>
+      </c>
+      <c r="L72" s="27" t="n">
+        <v>-13.26</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="D73" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="E73" s="27" t="n">
+        <v>26706.37</v>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>696.54</v>
+      </c>
+      <c r="G73" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="27" t="n">
+        <v>27402.91</v>
+      </c>
+      <c r="I73" s="27" t="n">
+        <v>2740.29</v>
+      </c>
+      <c r="J73" s="27" t="n">
+        <v>1335.32</v>
+      </c>
+      <c r="K73" s="27" t="n">
+        <v>1370.14</v>
+      </c>
+      <c r="L73" s="27" t="n">
+        <v>34.82</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E74" s="27" t="n">
+        <v>29349.09</v>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>625.82</v>
+      </c>
+      <c r="G74" s="27" t="n">
+        <v>-4915.77</v>
+      </c>
+      <c r="H74" s="27" t="n">
+        <v>25059.14</v>
+      </c>
+      <c r="I74" s="27" t="n">
+        <v>2505.91</v>
+      </c>
+      <c r="J74" s="27" t="n">
+        <v>709.74</v>
+      </c>
+      <c r="K74" s="27" t="n">
+        <v>715.98</v>
+      </c>
+      <c r="L74" s="27" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E75" s="27" t="n">
+        <v>17830</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>-224.55</v>
+      </c>
+      <c r="G75" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="27" t="n">
+        <v>17605.45</v>
+      </c>
+      <c r="I75" s="27" t="n">
+        <v>1760.55</v>
+      </c>
+      <c r="J75" s="27" t="n">
+        <v>777.86</v>
+      </c>
+      <c r="K75" s="27" t="n">
+        <v>880.27</v>
+      </c>
+      <c r="L75" s="27" t="n">
+        <v>102.41</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="E76" s="27" t="n">
+        <v>24315.45</v>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="G76" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="27" t="n">
+        <v>24651.18</v>
+      </c>
+      <c r="I76" s="27" t="n">
+        <v>2465.12</v>
+      </c>
+      <c r="J76" s="27" t="n">
+        <v>694.72</v>
+      </c>
+      <c r="K76" s="27" t="n">
+        <v>704.32</v>
+      </c>
+      <c r="L76" s="27" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="E77" s="27" t="n">
+        <v>24920.36</v>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="G77" s="27" t="n">
+        <v>-5088.48</v>
+      </c>
+      <c r="H77" s="27" t="n">
+        <v>20195.24</v>
+      </c>
+      <c r="I77" s="27" t="n">
+        <v>2019.52</v>
+      </c>
+      <c r="J77" s="27" t="n">
+        <v>881.53</v>
+      </c>
+      <c r="K77" s="27" t="n">
+        <v>1009.76</v>
+      </c>
+      <c r="L77" s="27" t="n">
+        <v>128.23</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="E78" s="27" t="n">
+        <v>25739.09</v>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="G78" s="27" t="n">
+        <v>-3741</v>
+      </c>
+      <c r="H78" s="27" t="n">
+        <v>22069.64</v>
+      </c>
+      <c r="I78" s="27" t="n">
+        <v>2206.96</v>
+      </c>
+      <c r="J78" s="27" t="n">
+        <v>2485.15</v>
+      </c>
+      <c r="K78" s="27" t="n">
+        <v>2206.96</v>
+      </c>
+      <c r="L78" s="27" t="n">
+        <v>-278.19</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="E79" s="27" t="n">
+        <v>26020.91</v>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="27" t="n">
+        <v>-3960.3</v>
+      </c>
+      <c r="H79" s="27" t="n">
+        <v>22060.61</v>
+      </c>
+      <c r="I79" s="27" t="n">
+        <v>2206.06</v>
+      </c>
+      <c r="J79" s="27" t="n">
+        <v>1976.73</v>
+      </c>
+      <c r="K79" s="27" t="n">
+        <v>1654.53</v>
+      </c>
+      <c r="L79" s="27" t="n">
+        <v>-322.2</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="8" t="n">
+        <f aca="false">SUM(E7:E79)</f>
+        <v>1744612.86</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <f aca="false">SUM(F7:F79)</f>
+        <v>-8381.89</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <f aca="false">SUM(G7:G79)</f>
+        <v>-101831.18</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <f aca="false">SUM(H7:H79)</f>
+        <v>1634399.79</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <f aca="false">SUM(I7:I79)</f>
+        <v>159376.25</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <f aca="false">SUM(J7:J79)</f>
+        <v>94602.32</v>
+      </c>
+      <c r="K80" s="8" t="n">
+        <f aca="false">SUM(K7:K79)</f>
+        <v>89284.04</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <f aca="false">SUM(L7:L79)</f>
+        <v>-5318.28</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="28" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="25"/>
+      <c r="B83" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="E83" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="25"/>
+      <c r="B84" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E84" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+      <c r="L84" s="25"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="25"/>
+      <c r="B85" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="D85" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="E85" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="25"/>
+      <c r="B86" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
+      <c r="H86" s="25"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="25"/>
+      <c r="B87" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="E87" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="25"/>
+      <c r="L87" s="25"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="25"/>
+      <c r="B88" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="D88" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
+      <c r="E88" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="25"/>
+      <c r="L88" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D19:K19"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="E83:L83"/>
+    <mergeCell ref="E84:L84"/>
+    <mergeCell ref="E85:L85"/>
+    <mergeCell ref="E86:L86"/>
+    <mergeCell ref="E87:L87"/>
+    <mergeCell ref="E88:L88"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4332,7 +6954,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4345,7 +6967,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>397</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4358,7 +6980,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>207</v>
+        <v>398</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -4377,7 +6999,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>28</v>
@@ -4392,24 +7014,24 @@
         <v>31</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>208</v>
+        <v>399</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>209</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>197</v>
+        <v>388</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>210</v>
+        <v>401</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>199</v>
+        <v>390</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>12</v>
@@ -4427,10 +7049,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>212</v>
+        <v>403</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>136</v>
@@ -4454,13 +7076,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>200</v>
+        <v>391</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>213</v>
+        <v>404</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>202</v>
+        <v>393</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>20</v>
@@ -4481,16 +7103,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>203</v>
+        <v>394</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>214</v>
+        <v>405</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>153</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>215</v>
+        <v>406</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>12</v>
@@ -4508,19 +7130,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>216</v>
+        <v>407</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>216</v>
+        <v>407</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>46</v>
@@ -4529,25 +7151,25 @@
         <v>35355</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3214.09</v>
+        <v>2670.3</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>217</v>
+        <v>408</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>218</v>
+        <v>409</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>46</v>
@@ -4556,19 +7178,19 @@
         <v>67927</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6175.18</v>
+        <v>6237.99</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>187</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>16</v>
@@ -4583,25 +7205,25 @@
         <v>19737</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1404.37</v>
+        <v>1807.56</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>46</v>
@@ -4610,25 +7232,25 @@
         <v>19737</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1794.27</v>
+        <v>1810.45</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>220</v>
+        <v>411</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>46</v>
@@ -4637,25 +7259,25 @@
         <v>23763</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2160.27</v>
+        <v>2204.65</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>222</v>
+        <v>413</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>46</v>
@@ -4664,7 +7286,7 @@
         <v>28945</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2631.36</v>
+        <v>2668.55</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -4679,10 +7301,10 @@
         <v>160</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>223</v>
+        <v>414</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>224</v>
+        <v>415</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>46</v>
@@ -4691,22 +7313,22 @@
         <v>7032</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>639.27</v>
+        <v>646.03</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>226</v>
+        <v>379</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>40</v>
@@ -4718,19 +7340,19 @@
         <v>28992</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2635.64</v>
+        <v>2206.04</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>229</v>
+        <v>375</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>230</v>
+        <v>376</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>231</v>
+        <v>377</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>16</v>
@@ -4745,25 +7367,25 @@
         <v>37273.2</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2485.15</v>
+        <v>2206.96</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>235</v>
+        <v>417</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
@@ -4772,25 +7394,25 @@
         <v>29100</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2204.25</v>
+        <v>2019.52</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>236</v>
+        <v>369</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>237</v>
+        <v>370</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>238</v>
+        <v>371</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>239</v>
+        <v>418</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>224</v>
+        <v>415</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>46</v>
@@ -4799,7 +7421,7 @@
         <v>26747</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2431.55</v>
+        <v>2465.12</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -4808,13 +7430,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>242</v>
+        <v>419</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>12</v>
@@ -4826,25 +7448,25 @@
         <v>17113</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1555.73</v>
+        <v>1760.54</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>244</v>
+        <v>366</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>245</v>
+        <v>420</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>246</v>
+        <v>421</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>46</v>
@@ -4853,22 +7475,22 @@
         <v>27325</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2484.09</v>
+        <v>2505.93</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>247</v>
+        <v>363</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>248</v>
+        <v>364</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>249</v>
+        <v>362</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>250</v>
+        <v>422</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>12</v>
@@ -4880,25 +7502,25 @@
         <v>29377</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2670.64</v>
+        <v>2740.28</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>249</v>
+        <v>362</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>253</v>
+        <v>423</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>254</v>
+        <v>424</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>46</v>
@@ -4907,22 +7529,22 @@
         <v>24878</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2261.64</v>
+        <v>2235.12</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>255</v>
+        <v>357</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>256</v>
+        <v>358</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>235</v>
+        <v>417</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>12</v>
@@ -4934,22 +7556,22 @@
         <v>23615</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2146.82</v>
+        <v>2733.84</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>250</v>
+        <v>422</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>15</v>
@@ -4961,19 +7583,19 @@
         <v>12925</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1175</v>
+        <v>1170.98</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>261</v>
+        <v>351</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>262</v>
+        <v>352</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>14</v>
@@ -4988,22 +7610,22 @@
         <v>16488</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1498.91</v>
+        <v>1501.24</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>264</v>
+        <v>348</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>12</v>
@@ -5015,19 +7637,19 @@
         <v>15439</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1403.55</v>
+        <v>1850.01</v>
       </c>
       <c r="I28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>268</v>
+        <v>346</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>15</v>
@@ -5042,19 +7664,19 @@
         <v>78848</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>7168</v>
+        <v>5519.28</v>
       </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>270</v>
+        <v>342</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>271</v>
+        <v>343</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>272</v>
+        <v>344</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>15</v>
@@ -5069,19 +7691,19 @@
         <v>45416.8</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>4128.8</v>
+        <v>3846.37</v>
       </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>273</v>
+        <v>339</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>63</v>
@@ -5096,19 +7718,19 @@
         <v>34986.6</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3180.6</v>
+        <v>3077.4</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>278</v>
+        <v>338</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>15</v>
@@ -5123,19 +7745,19 @@
         <v>26011.6</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2364.69</v>
+        <v>2141.89</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>280</v>
+        <v>334</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
@@ -5150,22 +7772,22 @@
         <v>35698.8</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1622.67</v>
+        <v>0</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>285</v>
+        <v>426</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>15</v>
@@ -5173,25 +7795,25 @@
       <c r="F34" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G34" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="28" t="n">
+      <c r="G34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>286</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>20</v>
@@ -5202,25 +7824,25 @@
       <c r="F35" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="28" t="n">
+      <c r="G35" s="29" t="n">
         <v>35000</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>289</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>63</v>
@@ -5235,25 +7857,25 @@
         <v>20594.6</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1872.24</v>
+        <v>1515.98</v>
       </c>
       <c r="I36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>294</v>
+        <v>429</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>46</v>
@@ -5268,19 +7890,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>46</v>
@@ -5289,25 +7911,25 @@
         <v>22668</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>2060.73</v>
+        <v>1836.8</v>
       </c>
       <c r="I38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>301</v>
+        <v>432</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>46</v>
@@ -5316,25 +7938,25 @@
         <v>31267.25</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>2842.48</v>
+        <v>2904.05</v>
       </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>305</v>
+        <v>433</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>46</v>
@@ -5343,25 +7965,25 @@
         <v>35548</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>3231.64</v>
+        <v>2717.95</v>
       </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>309</v>
+        <v>434</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>46</v>
@@ -5370,25 +7992,25 @@
         <v>24667</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2242.45</v>
+        <v>2195.1</v>
       </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>222</v>
+        <v>413</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>46</v>
@@ -5397,25 +8019,25 @@
         <v>22630</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>2057.27</v>
+        <v>2119.55</v>
       </c>
       <c r="I42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="D43" s="4" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>315</v>
+        <v>435</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>46</v>
@@ -5424,19 +8046,19 @@
         <v>36086</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>3280.55</v>
+        <v>3139.35</v>
       </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>12</v>
@@ -5451,19 +8073,19 @@
         <v>33761.6</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>3069.24</v>
+        <v>2770.87</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>63</v>
@@ -5478,25 +8100,25 @@
         <v>27025.4</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>2456.85</v>
+        <v>2074.44</v>
       </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>46</v>
@@ -5505,19 +8127,19 @@
         <v>19261.6</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1751.05</v>
+        <v>2680.92</v>
       </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>12</v>
@@ -5532,25 +8154,25 @@
         <v>53448.08</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>4858.92</v>
+        <v>4659.01</v>
       </c>
       <c r="I47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>46</v>
@@ -5559,25 +8181,25 @@
         <v>23526.6</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>2138.78</v>
+        <v>1995.52</v>
       </c>
       <c r="I48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>335</v>
+        <v>296</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>46</v>
@@ -5586,25 +8208,25 @@
         <v>29199.2</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>2654.47</v>
+        <v>2593.48</v>
       </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>339</v>
+        <v>440</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>340</v>
+        <v>441</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>46</v>
@@ -5613,25 +8235,25 @@
         <v>24250</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>2204.55</v>
+        <v>2099.04</v>
       </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>46</v>
@@ -5640,25 +8262,25 @@
         <v>38748.2</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3522.56</v>
+        <v>3036.72</v>
       </c>
       <c r="I51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>343</v>
+        <v>285</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>344</v>
+        <v>286</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>46</v>
@@ -5667,25 +8289,25 @@
         <v>32097.6</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>2917.96</v>
+        <v>3078.08</v>
       </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>346</v>
+        <v>288</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>46</v>
@@ -5694,19 +8316,19 @@
         <v>14851.2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1350.11</v>
+        <v>1442.48</v>
       </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>63</v>
@@ -5721,19 +8343,19 @@
         <v>71953.2</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>6541.2</v>
+        <v>6683.5</v>
       </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>352</v>
+        <v>280</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>15</v>
@@ -5748,25 +8370,25 @@
         <v>31049.2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>2822.65</v>
+        <v>2793.16</v>
       </c>
       <c r="I55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>355</v>
+        <v>277</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>356</v>
+        <v>278</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>46</v>
@@ -5775,25 +8397,25 @@
         <v>48152.8</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>4377.53</v>
+        <v>3708.36</v>
       </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>358</v>
+        <v>272</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>46</v>
@@ -5802,25 +8424,25 @@
         <v>30394.4</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>2763.13</v>
+        <v>2327.52</v>
       </c>
       <c r="I57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>361</v>
+        <v>275</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>46</v>
@@ -5829,25 +8451,25 @@
         <v>30114</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>2737.64</v>
+        <v>2359.86</v>
       </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>362</v>
+        <v>269</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>363</v>
+        <v>270</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>364</v>
+        <v>268</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>46</v>
@@ -5856,19 +8478,19 @@
         <v>27098.8</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>2463.53</v>
+        <v>2080.74</v>
       </c>
       <c r="I59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>365</v>
+        <v>266</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>366</v>
+        <v>267</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>364</v>
+        <v>268</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>15</v>
@@ -5883,22 +8505,22 @@
         <v>29890</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2717.27</v>
+        <v>2158.99</v>
       </c>
       <c r="I60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>367</v>
+        <v>263</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>368</v>
+        <v>264</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>20</v>
@@ -5910,19 +8532,19 @@
         <v>16511.6</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>750.53</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>371</v>
+        <v>260</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>372</v>
+        <v>261</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>63</v>
@@ -5937,19 +8559,19 @@
         <v>18139.6</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>1649.05</v>
+        <v>1663.18</v>
       </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>375</v>
+        <v>258</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>16</v>
@@ -5964,19 +8586,19 @@
         <v>19415.1</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>1118.11</v>
+        <v>1734.46</v>
       </c>
       <c r="I63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>377</v>
+        <v>254</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>15</v>
@@ -5991,19 +8613,19 @@
         <v>57409.2</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>5219.02</v>
+        <v>4978.64</v>
       </c>
       <c r="I64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>380</v>
+        <v>251</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>381</v>
+        <v>252</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>382</v>
+        <v>253</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>15</v>
@@ -6018,25 +8640,25 @@
         <v>36436.2</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>3312.38</v>
+        <v>3172.42</v>
       </c>
       <c r="I65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>383</v>
+        <v>248</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>384</v>
+        <v>249</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>385</v>
+        <v>250</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>46</v>
@@ -6045,19 +8667,19 @@
         <v>29420.2</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>2674.56</v>
+        <v>2708.16</v>
       </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>388</v>
+        <v>245</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>389</v>
+        <v>246</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>390</v>
+        <v>247</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>63</v>
@@ -6072,19 +8694,19 @@
         <v>12877.6</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>1170.69</v>
+        <v>1187.82</v>
       </c>
       <c r="I67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>391</v>
+        <v>242</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>392</v>
+        <v>243</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>393</v>
+        <v>244</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>63</v>
@@ -6099,19 +8721,19 @@
         <v>21878</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>1988.91</v>
+        <v>2075.95</v>
       </c>
       <c r="I68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>394</v>
+        <v>239</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>395</v>
+        <v>240</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>396</v>
+        <v>241</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>15</v>
@@ -6126,19 +8748,19 @@
         <v>15218</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>1383.45</v>
+        <v>1367.09</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>397</v>
+        <v>236</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>399</v>
+        <v>238</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>63</v>
@@ -6153,19 +8775,19 @@
         <v>5000</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>454.55</v>
+        <v>525</v>
       </c>
       <c r="I70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>400</v>
+        <v>233</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>401</v>
+        <v>234</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>402</v>
+        <v>235</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>63</v>
@@ -6180,19 +8802,19 @@
         <v>8175</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>743.18</v>
+        <v>767.36</v>
       </c>
       <c r="I71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
-        <v>403</v>
+        <v>230</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>404</v>
+        <v>231</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>405</v>
+        <v>232</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>15</v>
@@ -6207,25 +8829,25 @@
         <v>15535.6</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>1412.33</v>
+        <v>1447.84</v>
       </c>
       <c r="I72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>406</v>
+        <v>227</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>407</v>
+        <v>228</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>408</v>
+        <v>229</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>46</v>
@@ -6234,19 +8856,19 @@
         <v>22201</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>2018.27</v>
+        <v>2005.08</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>409</v>
+        <v>225</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>410</v>
+        <v>226</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>411</v>
+        <v>224</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>15</v>
@@ -6261,19 +8883,19 @@
         <v>10729</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>975.36</v>
+        <v>967.18</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>413</v>
+        <v>223</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>411</v>
+        <v>224</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>15</v>
@@ -6288,25 +8910,25 @@
         <v>13527.6</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>1229.78</v>
+        <v>1246.91</v>
       </c>
       <c r="I75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>414</v>
+        <v>219</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>415</v>
+        <v>220</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>416</v>
+        <v>221</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>46</v>
@@ -6315,22 +8937,22 @@
         <v>17583</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>1598.45</v>
+        <v>1590.27</v>
       </c>
       <c r="I76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>417</v>
+        <v>214</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>418</v>
+        <v>215</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>419</v>
+        <v>216</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>15</v>
@@ -6342,19 +8964,19 @@
         <v>4000</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>363.64</v>
+        <v>363.18</v>
       </c>
       <c r="I77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>420</v>
+        <v>217</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>421</v>
+        <v>218</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>419</v>
+        <v>216</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>15</v>
@@ -6369,19 +8991,19 @@
         <v>5000</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>454.55</v>
+        <v>272.27</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
-        <v>422</v>
+        <v>211</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>423</v>
+        <v>212</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>424</v>
+        <v>213</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>15</v>
@@ -6396,19 +9018,19 @@
         <v>5250</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>477.27</v>
+        <v>525</v>
       </c>
       <c r="I79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="s">
-        <v>425</v>
+        <v>208</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>426</v>
+        <v>209</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>427</v>
+        <v>210</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>15</v>
@@ -6423,19 +9045,19 @@
         <v>10000</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>909.09</v>
+        <v>999.5</v>
       </c>
       <c r="I80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>428</v>
+        <v>205</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>429</v>
+        <v>206</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>430</v>
+        <v>207</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>15</v>
@@ -6456,13 +9078,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>431</v>
+        <v>202</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>432</v>
+        <v>203</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>433</v>
+        <v>204</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>15</v>
@@ -6477,19 +9099,19 @@
         <v>20000</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>1818.18</v>
+        <v>1772.73</v>
       </c>
       <c r="I82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>434</v>
+        <v>199</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>435</v>
+        <v>200</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>436</v>
+        <v>201</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>15</v>
@@ -6504,19 +9126,19 @@
         <v>5000</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>454.55</v>
+        <v>272.27</v>
       </c>
       <c r="I83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>437</v>
+        <v>196</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>438</v>
+        <v>197</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>439</v>
+        <v>198</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>15</v>
@@ -6531,7 +9153,7 @@
         <v>5500</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>500</v>
+        <v>408.64</v>
       </c>
       <c r="I84" s="4"/>
     </row>
@@ -6550,7 +9172,7 @@
       </c>
       <c r="H85" s="8" t="n">
         <f aca="false">SUM(H6:H84)</f>
-        <v>172860.08</v>
+        <v>164861.31</v>
       </c>
       <c r="I85" s="7"/>
     </row>
@@ -6585,134 +9207,134 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>443</v>
+      <c r="A4" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
-        <v>444</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>445</v>
+      <c r="A5" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>446</v>
-      </c>
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>447</v>
+      <c r="B7" s="31" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>448</v>
+      <c r="B8" s="31" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>449</v>
+      <c r="B9" s="31" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>450</v>
+      <c r="B10" s="31" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="30" t="s">
-        <v>451</v>
+      <c r="B11" s="31" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>453</v>
+      <c r="A12" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="s">
-        <v>454</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>455</v>
+      <c r="A13" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="s">
-        <v>456</v>
-      </c>
-      <c r="B14" s="30" t="s">
+      <c r="A14" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="B14" s="31" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="s">
-        <v>457</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>458</v>
+      <c r="A15" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>460</v>
+      <c r="A16" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>462</v>
+      <c r="A17" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>463</v>
+      <c r="B18" s="31" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="473">
   <si>
     <t xml:space="preserve">Ampra Commission Tracker — Team Position</t>
   </si>
@@ -534,7 +534,7 @@
     <t xml:space="preserve">Reconciliation - confirmed commission vs estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Cycle 28/08/26 · every installed deal with all Xero figures confirmed · 77 reconciled, 3 not ready to pay</t>
+    <t xml:space="preserve">Cycle 28/08/26 · every installed deal with all Xero figures confirmed · 75 reconciled, 5 not ready to pay</t>
   </si>
   <si>
     <t xml:space="preserve">Net Revenue = Xero Revenue + ACP (Formbay) impact + Finance Fee impact, and is already GST-exclusive - it is never divided by 1.1. Commission Payable = 10% of Net Revenue, computed here rather than read from HubSpot: as at 26/08/26 the HubSpot field subtracts the ACP impact where Net Revenue adds it, so it is wrong on every deal with an ACP adjustment. Scott is correcting it at source. The pot is then split by the ordinary rules - Away by headcount, Home half to lead gen and half to specialist.</t>
@@ -750,466 +750,466 @@
     <t xml:space="preserve">28/01/26</t>
   </si>
   <si>
+    <t xml:space="preserve">SSA007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larry Grant - 77 Cecil Road Orange NSW 2800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Watt - 41 Milburn Place St Ives Chase NSW 2075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Cummins - 9 Waipori Street St Ives Chase NSW 2075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Rallings - 122 Eyles Drive East Ballina NSW 2478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria E Kelly - 2529 Pyramids Road Wyberba QLD 4382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Bob &amp; Lawson Muir - 1787 Delubngra Road Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Bob &amp; Lawson Muir - 1516 Delungra Road Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Heath - Unit 5 - 11 Prospect Street Mackay QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marion Priestly - 31 Adams Street Heddon Greta NSW 2321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Campbell - 11 Vesta Lane Ooralea QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vincent Reeves - 5 Lucy Court Mirani QLD 4754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Schaper - 22 Elizabeth Street Mirani QLD 4754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Boland - 16 Blackmur Street Marian QLD 4753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernie Shields - 9 Coral Drive Blacks Beach QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gibb French - 34 Alan Street Marian QLD 4753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Tooler - 8 Tranquil Place Alstonville NSW 2477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andy Callaway - 69 Maitland Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Dick - 36 Keera Street  Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annette Towers - 2 Finch Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dianne Burke - 91 Cunningham Street Bingara NSW 2404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosemary Arnold - 38 Holden Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Moore - 93 Stephen Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Campbell - 100 Dunwold-Cattle Creek Road Gargett QLD 4741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen Paskins - 11 Heathwood Court Hampden QLD 4741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rob Matta - 109 Brighton Street Croydon Park NSW 2133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henri Lago - 67 Amhurst Street Slade Point QLD 4740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy Wong - 10 O’Connor Street Eastlakes NSW 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210426.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serena Kash - 23 Crane Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040526.DWB03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Gray - 10 Cross Street  Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260426.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Hancock - 105 High Street Warialda NSW 2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230426.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felicity Menchin - 28 Inverell Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer Stewart - 3-5 Gleno Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer Stewart - 1 Gleno Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicki Davis - 36 Burnett Street Delungra NSW 2403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Woodmansey - 126-128 Hoddle Street Howlong NSW 2643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180526.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dee &amp; Steve Mansfield - 6 Rosewood Place Kyogle NSW 2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Jolly - 11 Ness Street Diamond Creek VIC 3089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allan Marks - 27 Hay Road Cable Beach WA 6726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mick Prokopiwskyi - 9 McMillan Court Newborough VIC 3825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ian Mcgrath - 6 Rivergum Avenue Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don Wood - 11 Pembroke Road Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160526.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christopher Hutton - 31 Boorabee Street Kyogle NSW 2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Currell - 37 Cameron Street Maclean NSW 2463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100626.JS02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee Achurch - 11 Myall Street Evans Head NSW 2473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosalee &amp; Greg Foran - 2 Bank Street Woodburn NSW 2471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130526.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daryl Boyd - 48 Martyn Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070426.DWB01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Moore - 6 Bank Street Woodburn NSW 2472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Craig Robinson- 14 Cedar Street Woodburn NSW 2472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190526.DWB04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverly &amp; Graeme Voss - 3 David Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230526.DWB02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry O'Farrell - 45 Frazer Street Ashford NSW 2361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100626.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgina Kelly - 21 Puertollano Place Broome WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristopher Iquin - 5 Euro Way Djugun WA 6725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120626.JS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebecca Hudson - 93 Main Street Clunes NSW 2480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT READY TO PAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dee &amp; Steve Mansfield - 206 Summerland Way Kyogle NSW  2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission Payable and Net Revenue both missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSA036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Mooney - 17 Philip Street South Golden Beach NSW 2483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installed 2026-04-17 but never signed off by finance — before the baseline, so not in the log and not payable</t>
+  </si>
+  <si>
     <t xml:space="preserve">SSA020</t>
   </si>
   <si>
     <t xml:space="preserve">Tony Tedesco - 7 Wasley Road Wasleys SA 5400</t>
   </si>
   <si>
-    <t xml:space="preserve">02/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larry Grant - 77 Cecil Road Orange NSW 2800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Watt - 41 Milburn Place St Ives Chase NSW 2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Cummins - 9 Waipori Street St Ives Chase NSW 2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Rallings - 122 Eyles Drive East Ballina NSW 2478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria E Kelly - 2529 Pyramids Road Wyberba QLD 4382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Bob &amp; Lawson Muir - 1787 Delubngra Road Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Bob &amp; Lawson Muir - 1516 Delungra Road Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Heath - Unit 5 - 11 Prospect Street Mackay QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marion Priestly - 31 Adams Street Heddon Greta NSW 2321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Campbell - 11 Vesta Lane Ooralea QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vincent Reeves - 5 Lucy Court Mirani QLD 4754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Schaper - 22 Elizabeth Street Mirani QLD 4754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Boland - 16 Blackmur Street Marian QLD 4753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bernie Shields - 9 Coral Drive Blacks Beach QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gibb French - 34 Alan Street Marian QLD 4753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Tooler - 8 Tranquil Place Alstonville NSW 2477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Mooney - 17 Philip Street South Golden Beach NSW 2483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andy Callaway - 69 Maitland Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrian Dick - 36 Keera Street  Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annette Towers - 2 Finch Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dianne Burke - 91 Cunningham Street Bingara NSW 2404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosemary Arnold - 38 Holden Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/04/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Moore - 93 Stephen Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Campbell - 100 Dunwold-Cattle Creek Road Gargett QLD 4741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allen Paskins - 11 Heathwood Court Hampden QLD 4741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rob Matta - 109 Brighton Street Croydon Park NSW 2133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henri Lago - 67 Amhurst Street Slade Point QLD 4740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amy Wong - 10 O’Connor Street Eastlakes NSW 2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210426.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serena Kash - 23 Crane Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040526.DWB03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Gray - 10 Cross Street  Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260426.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Hancock - 105 High Street Warialda NSW 2402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230426.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felicity Menchin - 28 Inverell Street Delungra NSW 2403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer Stewart - 3-5 Gleno Street Delungra NSW 2403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer Stewart - 1 Gleno Street Delungra NSW 2403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicki Davis - 36 Burnett Street Delungra NSW 2403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Woodmansey - 126-128 Hoddle Street Howlong NSW 2643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180526.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dee &amp; Steve Mansfield - 6 Rosewood Place Kyogle NSW 2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Jolly - 11 Ness Street Diamond Creek VIC 3089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allan Marks - 27 Hay Road Cable Beach WA 6726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mick Prokopiwskyi - 9 McMillan Court Newborough VIC 3825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ian Mcgrath - 6 Rivergum Avenue Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don Wood - 11 Pembroke Road Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160526.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christopher Hutton - 31 Boorabee Street Kyogle NSW 2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adrian Currell - 37 Cameron Street Maclean NSW 2463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/06/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100626.JS02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee Achurch - 11 Myall Street Evans Head NSW 2473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosalee &amp; Greg Foran - 2 Bank Street Woodburn NSW 2471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130526.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daryl Boyd - 48 Martyn Street Ashford NSW 2361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070426.DWB01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Moore - 6 Bank Street Woodburn NSW 2472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Craig Robinson- 14 Cedar Street Woodburn NSW 2472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190526.DWB04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverly &amp; Graeme Voss - 3 David Street Ashford NSW 2361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230526.DWB02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barry O'Farrell - 45 Frazer Street Ashford NSW 2361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100626.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgina Kelly - 21 Puertollano Place Broome WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSA039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristopher Iquin - 5 Euro Way Djugun WA 6725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120626.JS01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebecca Hudson - 93 Main Street Clunes NSW 2480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT READY TO PAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dee &amp; Steve Mansfield - 206 Summerland Way Kyogle NSW  2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commission Payable and Net Revenue both missing</t>
+    <t xml:space="preserve">Installed 2026-02-02 but never signed off by finance — before the baseline, so not in the log and not payable</t>
   </si>
   <si>
     <t xml:space="preserve">SSA037</t>
@@ -1230,7 +1230,7 @@
     <t xml:space="preserve">Installed Deals Log — installed before 20/07/26</t>
   </si>
   <si>
-    <t xml:space="preserve">81 deals · reference only, not counted in current positions · pull 28/08/26</t>
+    <t xml:space="preserve">75 deals · reference only, not counted in current positions · pull 28/08/26</t>
   </si>
   <si>
     <t xml:space="preserve">Estimate up to 20/07/26. Figures before that date are reconstructed from HubSpot and contain known inconsistencies — 0 rows flagged below have no install date, no deal value, or no attribution recorded. Commission shown is earned/owed on install, not cash paid. Treat these totals as an estimate for cross-referencing, not a settled ledger.</t>
@@ -1257,73 +1257,70 @@
     <t xml:space="preserve">Flag</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Bradfield; Hugo; Hannah; Denzel Winterbeard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Mark Isaac; Max Bradfield; Hugo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosa; Dermot; Hugo; Max Bradfield; Denzel Winterbeard; Cian Jefferson; Fran; Hannah; Joe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Rosa; Dermot; Fran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Mark Isaac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo; Mark Isaac; Max Bradfield; Cian Jefferson; Denzel Winterbeard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Hugo; Max Bradfield; Mark Isaac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fran; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Dermot; Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Dermot; Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cian Jefferson; Denzel Winterbeard; Max Bradfield; Hugo; Mark Isaac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cian Jefferson; Hugo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cian Jefferson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Hugo; Max Bradfield; Rosa; Dermot; Fran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosa; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Rosa; Dermot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Mark Isaac; Joe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cian Jefferson; Denzel Winterbeard; Max Bradfield; Hugo; Mark Isaac; Joe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fran</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beau Jolly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/08/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Bradfield; Hugo; Hannah; Denzel Winterbeard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Mark Isaac; Max Bradfield; Hugo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosa; Dermot; Hugo; Max Bradfield; Denzel Winterbeard; Cian Jefferson; Fran; Hannah; Joe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Rosa; Dermot; Fran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Mark Isaac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo; Mark Isaac; Max Bradfield; Cian Jefferson; Denzel Winterbeard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Hugo; Max Bradfield; Mark Isaac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fran; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Dermot; Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Dermot; Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cian Jefferson; Denzel Winterbeard; Max Bradfield; Hugo; Mark Isaac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cian Jefferson; Hugo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cian Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Hugo; Max Bradfield; Rosa; Dermot; Fran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosa; Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Fran; Rosa; Dermot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denzel Winterbeard; Cian Jefferson; Max Bradfield; Hugo; Mark Isaac; Joe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cian Jefferson; Denzel Winterbeard; Max Bradfield; Hugo; Mark Isaac; Joe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fran</t>
   </si>
   <si>
     <t xml:space="preserve">Joe; Dermot</t>
@@ -1573,7 +1570,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF7A5450"/>
+      <color rgb="FF166B42"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1581,7 +1578,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF166B42"/>
+      <color rgb="FF7A5450"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -4799,7 +4796,7 @@
         <v>243</v>
       </c>
       <c r="E29" s="23" t="n">
-        <v>7673.64</v>
+        <v>5250</v>
       </c>
       <c r="F29" s="23" t="n">
         <v>0</v>
@@ -4808,16 +4805,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>7673.64</v>
+        <v>5250</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>743.18</v>
+        <v>1000</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K29" s="23" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L29" s="23" t="n">
         <v>0</v>
@@ -4837,25 +4834,25 @@
         <v>246</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>5250</v>
+        <v>14318.18</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>0</v>
+        <v>-647.27</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>5250</v>
+        <v>13670.91</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>1000</v>
+        <v>1367.09</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>500</v>
+        <v>1367.09</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>500</v>
+        <v>1367.09</v>
       </c>
       <c r="L30" s="23" t="n">
         <v>0</v>
@@ -4875,25 +4872,25 @@
         <v>249</v>
       </c>
       <c r="E31" s="23" t="n">
-        <v>14318.18</v>
+        <v>19359.09</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>-647.27</v>
+        <v>1400.45</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>13670.91</v>
+        <v>20759.54</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>1367.09</v>
+        <v>2225</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>1367.09</v>
+        <v>1112.5</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>1367.09</v>
+        <v>1112.5</v>
       </c>
       <c r="L31" s="23" t="n">
         <v>0</v>
@@ -4913,25 +4910,25 @@
         <v>252</v>
       </c>
       <c r="E32" s="23" t="n">
-        <v>19359.09</v>
+        <v>11706.91</v>
       </c>
       <c r="F32" s="23" t="n">
-        <v>1400.45</v>
+        <v>171.27</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>20759.54</v>
+        <v>11878.18</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>2225</v>
+        <v>1100</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>1112.5</v>
+        <v>550</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>1112.5</v>
+        <v>550</v>
       </c>
       <c r="L32" s="23" t="n">
         <v>0</v>
@@ -4951,25 +4948,25 @@
         <v>255</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>11706.91</v>
+        <v>26744.73</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>171.27</v>
+        <v>336.09</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>11878.18</v>
+        <v>27080.82</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>1100</v>
+        <v>2708.08</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>550</v>
+        <v>1805.38</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>550</v>
+        <v>1805.38</v>
       </c>
       <c r="L33" s="23" t="n">
         <v>0</v>
@@ -4989,25 +4986,25 @@
         <v>258</v>
       </c>
       <c r="E34" s="23" t="n">
-        <v>26744.73</v>
+        <v>33123.82</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>336.09</v>
+        <v>3526</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>0</v>
+        <v>-5336.37</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>27080.82</v>
+        <v>31313.45</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>2708.08</v>
+        <v>3131.35</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>1805.38</v>
+        <v>3131.35</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>1805.38</v>
+        <v>3131.35</v>
       </c>
       <c r="L34" s="23" t="n">
         <v>0</v>
@@ -5027,25 +5024,25 @@
         <v>261</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>33123.82</v>
+        <v>50870.91</v>
       </c>
       <c r="F35" s="23" t="n">
-        <v>3526</v>
+        <v>3168.36</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-5336.37</v>
+        <v>-9859.18</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>31313.45</v>
+        <v>44180.09</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>3131.35</v>
+        <v>4418.01</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>3131.35</v>
+        <v>4418.01</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>3131.35</v>
+        <v>4418.01</v>
       </c>
       <c r="L35" s="23" t="n">
         <v>0</v>
@@ -5065,25 +5062,25 @@
         <v>264</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>50870.91</v>
+        <v>17844.55</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>3168.36</v>
+        <v>-500</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>-9859.18</v>
+        <v>0</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>44180.09</v>
+        <v>17344.55</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>4418.01</v>
+        <v>1734.46</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>4418.01</v>
+        <v>1734.46</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>4418.01</v>
+        <v>1734.46</v>
       </c>
       <c r="L36" s="23" t="n">
         <v>0</v>
@@ -5103,25 +5100,25 @@
         <v>267</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>17844.55</v>
+        <v>17268.18</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>-500</v>
+        <v>-636.36</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>17344.55</v>
+        <v>16631.82</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>1734.46</v>
+        <v>1663.18</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>1734.46</v>
+        <v>0</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>1734.46</v>
+        <v>0</v>
       </c>
       <c r="L37" s="23" t="n">
         <v>0</v>
@@ -5141,19 +5138,19 @@
         <v>270</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>17268.18</v>
+        <v>20250</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>-636.36</v>
+        <v>-5207.27</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>16631.82</v>
+        <v>15042.73</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>1663.18</v>
+        <v>0</v>
       </c>
       <c r="J38" s="23" t="n">
         <v>0</v>
@@ -5179,25 +5176,25 @@
         <v>273</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>20250</v>
+        <v>24076.18</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>-5207.27</v>
+        <v>-899.82</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>0</v>
+        <v>-2451.07</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>15042.73</v>
+        <v>20725.29</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>0</v>
+        <v>2072.53</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>0</v>
+        <v>690.84</v>
       </c>
       <c r="K39" s="23" t="n">
-        <v>0</v>
+        <v>690.84</v>
       </c>
       <c r="L39" s="23" t="n">
         <v>0</v>
@@ -5214,28 +5211,28 @@
         <v>275</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>24076.18</v>
+        <v>22776.37</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>-899.82</v>
+        <v>2040.91</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>-2451.07</v>
+        <v>-3496.51</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>20725.29</v>
+        <v>21320.77</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>2072.53</v>
+        <v>2132.08</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>690.84</v>
+        <v>2132.08</v>
       </c>
       <c r="K40" s="23" t="n">
-        <v>690.84</v>
+        <v>2132.08</v>
       </c>
       <c r="L40" s="23" t="n">
         <v>0</v>
@@ -5246,34 +5243,34 @@
         <v>203</v>
       </c>
       <c r="B41" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="D41" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>276</v>
-      </c>
       <c r="E41" s="23" t="n">
-        <v>22776.37</v>
+        <v>28526.55</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>2040.91</v>
+        <v>-1460.73</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>-3496.51</v>
+        <v>-3466.87</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>21320.77</v>
+        <v>23598.95</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>2132.08</v>
+        <v>2359.9</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>2132.08</v>
+        <v>786.64</v>
       </c>
       <c r="K41" s="23" t="n">
-        <v>2132.08</v>
+        <v>786.64</v>
       </c>
       <c r="L41" s="23" t="n">
         <v>0</v>
@@ -5290,28 +5287,28 @@
         <v>280</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E42" s="23" t="n">
-        <v>28526.55</v>
+        <v>30136.37</v>
       </c>
       <c r="F42" s="23" t="n">
-        <v>-1460.73</v>
+        <v>-3362.18</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>-3466.87</v>
+        <v>-3790.81</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>23598.95</v>
+        <v>22983.38</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>2359.9</v>
+        <v>2298.34</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>786.64</v>
+        <v>766.12</v>
       </c>
       <c r="K42" s="23" t="n">
-        <v>786.64</v>
+        <v>766.12</v>
       </c>
       <c r="L42" s="23" t="n">
         <v>0</v>
@@ -5322,34 +5319,34 @@
         <v>203</v>
       </c>
       <c r="B43" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="D43" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>281</v>
-      </c>
       <c r="E43" s="23" t="n">
-        <v>30136.37</v>
+        <v>43775.27</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>-3362.18</v>
+        <v>-375.09</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>-3790.81</v>
+        <v>-6842.94</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>22983.38</v>
+        <v>36557.24</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>2298.34</v>
+        <v>3655.72</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>766.12</v>
+        <v>1218.58</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>766.12</v>
+        <v>1218.58</v>
       </c>
       <c r="L43" s="23" t="n">
         <v>0</v>
@@ -5369,25 +5366,25 @@
         <v>286</v>
       </c>
       <c r="E44" s="23" t="n">
-        <v>43775.27</v>
+        <v>28636.36</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>-375.09</v>
+        <v>-704.72</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>-6842.94</v>
+        <v>0</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>36557.24</v>
+        <v>27931.64</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>3655.72</v>
+        <v>2793.16</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>1218.58</v>
+        <v>1396.58</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>1218.58</v>
+        <v>1396.58</v>
       </c>
       <c r="L44" s="23" t="n">
         <v>0</v>
@@ -5407,25 +5404,25 @@
         <v>289</v>
       </c>
       <c r="E45" s="23" t="n">
-        <v>28636.36</v>
+        <v>30709.09</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>-704.72</v>
+        <v>71.82</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>27931.64</v>
+        <v>30780.91</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>2793.16</v>
+        <v>3078.09</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>1396.58</v>
+        <v>769.52</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>1396.58</v>
+        <v>769.52</v>
       </c>
       <c r="L45" s="23" t="n">
         <v>0</v>
@@ -5442,28 +5439,28 @@
         <v>291</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E46" s="23" t="n">
-        <v>65188.18</v>
+        <v>13304.54</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>1646.82</v>
+        <v>1120.37</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>66835</v>
+        <v>14424.91</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>6541.2</v>
+        <v>1442.49</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>3270.6</v>
+        <v>360.62</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>3270.6</v>
+        <v>360.62</v>
       </c>
       <c r="L46" s="23" t="n">
         <v>0</v>
@@ -5474,34 +5471,34 @@
         <v>203</v>
       </c>
       <c r="B47" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="D47" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>295</v>
-      </c>
       <c r="E47" s="23" t="n">
-        <v>30709.09</v>
+        <v>37204.55</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>71.82</v>
+        <v>-3412.73</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>0</v>
+        <v>-3506.34</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>30780.91</v>
+        <v>30285.48</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>3078.09</v>
+        <v>3028.55</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>769.52</v>
+        <v>757.14</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>769.52</v>
+        <v>757.14</v>
       </c>
       <c r="L47" s="23" t="n">
         <v>0</v>
@@ -5512,34 +5509,34 @@
         <v>203</v>
       </c>
       <c r="B48" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="C48" s="21" t="s">
-        <v>297</v>
-      </c>
       <c r="D48" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E48" s="23" t="n">
-        <v>13304.54</v>
+        <v>21751.81</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>1120.37</v>
+        <v>-761.36</v>
       </c>
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="23" t="n">
-        <v>14424.91</v>
+        <v>20990.45</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>1442.49</v>
+        <v>2099.05</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>360.62</v>
+        <v>1049.52</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>360.62</v>
+        <v>1049.52</v>
       </c>
       <c r="L48" s="23" t="n">
         <v>0</v>
@@ -5550,34 +5547,34 @@
         <v>203</v>
       </c>
       <c r="B49" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="D49" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="D49" s="21" t="s">
-        <v>300</v>
-      </c>
       <c r="E49" s="23" t="n">
-        <v>37204.55</v>
+        <v>20408.18</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>-3412.73</v>
+        <v>993.64</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>-3506.34</v>
+        <v>-1528.34</v>
       </c>
       <c r="H49" s="23" t="n">
-        <v>30285.48</v>
+        <v>19873.48</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>3028.55</v>
+        <v>1987.35</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>757.14</v>
+        <v>496.84</v>
       </c>
       <c r="K49" s="23" t="n">
-        <v>757.14</v>
+        <v>496.84</v>
       </c>
       <c r="L49" s="23" t="n">
         <v>0</v>
@@ -5588,34 +5585,34 @@
         <v>203</v>
       </c>
       <c r="B50" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C50" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="C50" s="21" t="s">
-        <v>302</v>
-      </c>
       <c r="D50" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E50" s="23" t="n">
-        <v>21751.81</v>
+        <v>26544.73</v>
       </c>
       <c r="F50" s="23" t="n">
-        <v>-761.36</v>
+        <v>-610</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="23" t="n">
-        <v>20990.45</v>
+        <v>25934.73</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>2099.05</v>
+        <v>2593.47</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>1049.52</v>
+        <v>648.37</v>
       </c>
       <c r="K50" s="23" t="n">
-        <v>1049.52</v>
+        <v>648.37</v>
       </c>
       <c r="L50" s="23" t="n">
         <v>0</v>
@@ -5626,34 +5623,34 @@
         <v>203</v>
       </c>
       <c r="B51" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="D51" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>305</v>
-      </c>
       <c r="E51" s="23" t="n">
-        <v>20408.18</v>
+        <v>52279.51</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>993.64</v>
+        <v>-5689.37</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>-1528.34</v>
+        <v>0</v>
       </c>
       <c r="H51" s="23" t="n">
-        <v>19873.48</v>
+        <v>46590.14</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>1987.35</v>
+        <v>4659.01</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>496.84</v>
+        <v>4659.01</v>
       </c>
       <c r="K51" s="23" t="n">
-        <v>496.84</v>
+        <v>4659.01</v>
       </c>
       <c r="L51" s="23" t="n">
         <v>0</v>
@@ -5664,34 +5661,34 @@
         <v>203</v>
       </c>
       <c r="B52" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C52" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="D52" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>305</v>
-      </c>
       <c r="E52" s="23" t="n">
-        <v>26544.73</v>
+        <v>25261</v>
       </c>
       <c r="F52" s="23" t="n">
-        <v>-610</v>
+        <v>1548.55</v>
       </c>
       <c r="G52" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="23" t="n">
-        <v>25934.73</v>
+        <v>26809.55</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>2593.47</v>
+        <v>2680.96</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>648.37</v>
+        <v>893.66</v>
       </c>
       <c r="K52" s="23" t="n">
-        <v>648.37</v>
+        <v>893.66</v>
       </c>
       <c r="L52" s="23" t="n">
         <v>0</v>
@@ -5708,28 +5705,28 @@
         <v>309</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E53" s="23" t="n">
-        <v>52279.51</v>
+        <v>25545.45</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>-5689.37</v>
+        <v>-4801.09</v>
       </c>
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="23" t="n">
-        <v>46590.14</v>
+        <v>20744.36</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>4659.01</v>
+        <v>2074.44</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>4659.01</v>
+        <v>1037.22</v>
       </c>
       <c r="K53" s="23" t="n">
-        <v>4659.01</v>
+        <v>1037.22</v>
       </c>
       <c r="L53" s="23" t="n">
         <v>0</v>
@@ -5740,34 +5737,34 @@
         <v>203</v>
       </c>
       <c r="B54" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="C54" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="C54" s="21" t="s">
-        <v>312</v>
-      </c>
       <c r="D54" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="23" t="n">
-        <v>25261</v>
+        <v>23826.93</v>
       </c>
       <c r="F54" s="23" t="n">
-        <v>1548.55</v>
+        <v>53.07</v>
       </c>
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="23" t="n">
-        <v>26809.55</v>
+        <v>23880</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>2680.96</v>
+        <v>2388</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>893.66</v>
+        <v>2388</v>
       </c>
       <c r="K54" s="23" t="n">
-        <v>893.66</v>
+        <v>2388</v>
       </c>
       <c r="L54" s="23" t="n">
         <v>0</v>
@@ -5778,34 +5775,34 @@
         <v>203</v>
       </c>
       <c r="B55" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="C55" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>313</v>
-      </c>
       <c r="E55" s="23" t="n">
-        <v>25545.45</v>
+        <v>27253.63</v>
       </c>
       <c r="F55" s="23" t="n">
-        <v>-4801.09</v>
+        <v>455.09</v>
       </c>
       <c r="G55" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>20744.36</v>
+        <v>27708.72</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>2074.44</v>
+        <v>2770.87</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>1037.22</v>
+        <v>2770.87</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>1037.22</v>
+        <v>2770.87</v>
       </c>
       <c r="L55" s="23" t="n">
         <v>0</v>
@@ -5816,34 +5813,34 @@
         <v>203</v>
       </c>
       <c r="B56" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="D56" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="D56" s="21" t="s">
-        <v>313</v>
-      </c>
       <c r="E56" s="23" t="n">
-        <v>23826.93</v>
+        <v>30827.27</v>
       </c>
       <c r="F56" s="23" t="n">
-        <v>53.07</v>
+        <v>566</v>
       </c>
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="23" t="n">
-        <v>23880</v>
+        <v>31393.27</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>2388</v>
+        <v>3139.33</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>2388</v>
+        <v>1255.74</v>
       </c>
       <c r="K56" s="23" t="n">
-        <v>2388</v>
+        <v>1255.74</v>
       </c>
       <c r="L56" s="23" t="n">
         <v>0</v>
@@ -5863,25 +5860,25 @@
         <v>320</v>
       </c>
       <c r="E57" s="23" t="n">
-        <v>27253.63</v>
+        <v>22090</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>455.09</v>
+        <v>-138.91</v>
       </c>
       <c r="G57" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="23" t="n">
-        <v>27708.72</v>
+        <v>21951.09</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>2770.87</v>
+        <v>2195.11</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>2770.87</v>
+        <v>878.04</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>2770.87</v>
+        <v>878.04</v>
       </c>
       <c r="L57" s="23" t="n">
         <v>0</v>
@@ -5898,28 +5895,28 @@
         <v>322</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E58" s="23" t="n">
-        <v>30827.27</v>
+        <v>20118.18</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>566</v>
+        <v>1077.09</v>
       </c>
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="23" t="n">
-        <v>31393.27</v>
+        <v>21195.27</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>3139.33</v>
+        <v>2119.53</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>1255.74</v>
+        <v>847.82</v>
       </c>
       <c r="K58" s="23" t="n">
-        <v>1255.74</v>
+        <v>847.82</v>
       </c>
       <c r="L58" s="23" t="n">
         <v>0</v>
@@ -5930,34 +5927,34 @@
         <v>203</v>
       </c>
       <c r="B59" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="D59" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>326</v>
-      </c>
       <c r="E59" s="23" t="n">
-        <v>22090</v>
+        <v>33354.55</v>
       </c>
       <c r="F59" s="23" t="n">
-        <v>-138.91</v>
+        <v>-949.8</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>0</v>
+        <v>-5225.2</v>
       </c>
       <c r="H59" s="23" t="n">
-        <v>21951.09</v>
+        <v>27179.55</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>2195.11</v>
+        <v>2717.96</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>878.04</v>
+        <v>1087.18</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>878.04</v>
+        <v>1087.18</v>
       </c>
       <c r="L59" s="23" t="n">
         <v>0</v>
@@ -5968,34 +5965,34 @@
         <v>203</v>
       </c>
       <c r="B60" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="C60" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="D60" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>326</v>
-      </c>
       <c r="E60" s="23" t="n">
-        <v>20118.18</v>
+        <v>34665.68</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>1077.09</v>
+        <v>0</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>0</v>
+        <v>-5624.98</v>
       </c>
       <c r="H60" s="23" t="n">
-        <v>21195.27</v>
+        <v>29040.7</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>2119.53</v>
+        <v>2904.07</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>847.82</v>
+        <v>1161.62</v>
       </c>
       <c r="K60" s="23" t="n">
-        <v>847.82</v>
+        <v>1161.62</v>
       </c>
       <c r="L60" s="23" t="n">
         <v>0</v>
@@ -6006,34 +6003,34 @@
         <v>203</v>
       </c>
       <c r="B61" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="C61" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="21" t="s">
-        <v>330</v>
-      </c>
       <c r="D61" s="21" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E61" s="23" t="n">
-        <v>33354.55</v>
+        <v>34665.68</v>
       </c>
       <c r="F61" s="23" t="n">
-        <v>-949.8</v>
+        <v>922.36</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>-5225.2</v>
+        <v>-5624.99</v>
       </c>
       <c r="H61" s="23" t="n">
-        <v>27179.55</v>
+        <v>29963.05</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>2717.96</v>
+        <v>2996.31</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>1087.18</v>
+        <v>1198.52</v>
       </c>
       <c r="K61" s="23" t="n">
-        <v>1087.18</v>
+        <v>1198.52</v>
       </c>
       <c r="L61" s="23" t="n">
         <v>0</v>
@@ -6044,34 +6041,34 @@
         <v>203</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E62" s="23" t="n">
-        <v>34665.68</v>
+        <v>21516.36</v>
       </c>
       <c r="F62" s="23" t="n">
-        <v>0</v>
+        <v>-1332.18</v>
       </c>
       <c r="G62" s="23" t="n">
-        <v>-5624.98</v>
+        <v>-3148.25</v>
       </c>
       <c r="H62" s="23" t="n">
-        <v>29040.7</v>
+        <v>17035.93</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>2904.07</v>
+        <v>1703.59</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>1161.62</v>
+        <v>681.44</v>
       </c>
       <c r="K62" s="23" t="n">
-        <v>1161.62</v>
+        <v>681.44</v>
       </c>
       <c r="L62" s="23" t="n">
         <v>0</v>
@@ -6085,31 +6082,31 @@
         <v>332</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D63" s="21" t="s">
         <v>334</v>
       </c>
       <c r="E63" s="23" t="n">
-        <v>34665.68</v>
+        <v>19500</v>
       </c>
       <c r="F63" s="23" t="n">
-        <v>922.36</v>
+        <v>-2419.64</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>-5624.99</v>
+        <v>-1920.55</v>
       </c>
       <c r="H63" s="23" t="n">
-        <v>29963.05</v>
+        <v>15159.81</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>2996.31</v>
+        <v>2200</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>1198.52</v>
+        <v>1100</v>
       </c>
       <c r="K63" s="23" t="n">
-        <v>1198.52</v>
+        <v>1100</v>
       </c>
       <c r="L63" s="23" t="n">
         <v>0</v>
@@ -6120,34 +6117,34 @@
         <v>203</v>
       </c>
       <c r="B64" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="C64" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="D64" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="D64" s="21" t="s">
-        <v>334</v>
-      </c>
       <c r="E64" s="23" t="n">
-        <v>21516.36</v>
+        <v>41930</v>
       </c>
       <c r="F64" s="23" t="n">
-        <v>-1332.18</v>
+        <v>1210.09</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>-3148.25</v>
+        <v>0</v>
       </c>
       <c r="H64" s="23" t="n">
-        <v>17035.93</v>
+        <v>43140.09</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>1703.59</v>
+        <v>4314.01</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>681.44</v>
+        <v>3235.51</v>
       </c>
       <c r="K64" s="23" t="n">
-        <v>681.44</v>
+        <v>3235.51</v>
       </c>
       <c r="L64" s="23" t="n">
         <v>0</v>
@@ -6167,25 +6164,25 @@
         <v>340</v>
       </c>
       <c r="E65" s="23" t="n">
-        <v>19500</v>
+        <v>25390</v>
       </c>
       <c r="F65" s="23" t="n">
-        <v>-2419.64</v>
+        <v>204.37</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>-1920.55</v>
+        <v>0</v>
       </c>
       <c r="H65" s="23" t="n">
-        <v>15159.81</v>
+        <v>25594.37</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="K65" s="23" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="L65" s="23" t="n">
         <v>0</v>
@@ -6205,25 +6202,25 @@
         <v>343</v>
       </c>
       <c r="E66" s="23" t="n">
-        <v>41930</v>
+        <v>21468.18</v>
       </c>
       <c r="F66" s="23" t="n">
-        <v>1210.09</v>
+        <v>-49.27</v>
       </c>
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="23" t="n">
-        <v>43140.09</v>
+        <v>21418.91</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>4314.01</v>
+        <v>2141.89</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>3235.51</v>
+        <v>1070.94</v>
       </c>
       <c r="K66" s="23" t="n">
-        <v>3235.51</v>
+        <v>1070.94</v>
       </c>
       <c r="L66" s="23" t="n">
         <v>0</v>
@@ -6243,19 +6240,19 @@
         <v>346</v>
       </c>
       <c r="E67" s="23" t="n">
-        <v>25390</v>
+        <v>31957.27</v>
       </c>
       <c r="F67" s="23" t="n">
-        <v>204.37</v>
+        <v>-1183.27</v>
       </c>
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="23" t="n">
-        <v>25594.37</v>
+        <v>30774</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>0</v>
+        <v>3077.4</v>
       </c>
       <c r="J67" s="23" t="n">
         <v>0</v>
@@ -6281,25 +6278,25 @@
         <v>349</v>
       </c>
       <c r="E68" s="23" t="n">
-        <v>21468.18</v>
+        <v>44461.82</v>
       </c>
       <c r="F68" s="23" t="n">
-        <v>-49.27</v>
+        <v>989.09</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>0</v>
+        <v>-6987.25</v>
       </c>
       <c r="H68" s="23" t="n">
-        <v>21418.91</v>
+        <v>38463.66</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>2141.89</v>
+        <v>3846.37</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>1070.94</v>
+        <v>3846.37</v>
       </c>
       <c r="K68" s="23" t="n">
-        <v>1070.94</v>
+        <v>3846.37</v>
       </c>
       <c r="L68" s="23" t="n">
         <v>0</v>
@@ -6319,25 +6316,25 @@
         <v>352</v>
       </c>
       <c r="E69" s="23" t="n">
-        <v>31957.27</v>
+        <v>63424.55</v>
       </c>
       <c r="F69" s="23" t="n">
-        <v>-1183.27</v>
+        <v>1616</v>
       </c>
       <c r="G69" s="23" t="n">
-        <v>0</v>
+        <v>-9847.73</v>
       </c>
       <c r="H69" s="23" t="n">
-        <v>30774</v>
+        <v>55192.82</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>3077.4</v>
+        <v>5519.28</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>0</v>
+        <v>5519.28</v>
       </c>
       <c r="K69" s="23" t="n">
-        <v>0</v>
+        <v>5519.28</v>
       </c>
       <c r="L69" s="23" t="n">
         <v>0</v>
@@ -6357,25 +6354,25 @@
         <v>355</v>
       </c>
       <c r="E70" s="23" t="n">
-        <v>44461.82</v>
+        <v>18519.3</v>
       </c>
       <c r="F70" s="23" t="n">
-        <v>989.09</v>
+        <v>-19.27</v>
       </c>
       <c r="G70" s="23" t="n">
-        <v>-6987.25</v>
+        <v>0</v>
       </c>
       <c r="H70" s="23" t="n">
-        <v>38463.66</v>
+        <v>18500.03</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>3846.37</v>
+        <v>1850</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>3846.37</v>
+        <v>1233.34</v>
       </c>
       <c r="K70" s="23" t="n">
-        <v>3846.37</v>
+        <v>1233.34</v>
       </c>
       <c r="L70" s="23" t="n">
         <v>0</v>
@@ -6395,25 +6392,25 @@
         <v>358</v>
       </c>
       <c r="E71" s="23" t="n">
-        <v>63424.55</v>
+        <v>14989.09</v>
       </c>
       <c r="F71" s="23" t="n">
-        <v>1616</v>
+        <v>23.27</v>
       </c>
       <c r="G71" s="23" t="n">
-        <v>-9847.73</v>
+        <v>0</v>
       </c>
       <c r="H71" s="23" t="n">
-        <v>55192.82</v>
+        <v>15012.36</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>5519.28</v>
+        <v>1501.24</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>5519.28</v>
+        <v>1501.24</v>
       </c>
       <c r="K71" s="23" t="n">
-        <v>5519.28</v>
+        <v>1501.24</v>
       </c>
       <c r="L71" s="23" t="n">
         <v>0</v>
@@ -6433,25 +6430,25 @@
         <v>361</v>
       </c>
       <c r="E72" s="23" t="n">
-        <v>18519.3</v>
+        <v>11750</v>
       </c>
       <c r="F72" s="23" t="n">
-        <v>-19.27</v>
+        <v>-40.23</v>
       </c>
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="23" t="n">
-        <v>18500.03</v>
+        <v>11709.77</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>1850</v>
+        <v>1170.98</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>1233.34</v>
+        <v>585.49</v>
       </c>
       <c r="K72" s="23" t="n">
-        <v>1233.34</v>
+        <v>585.49</v>
       </c>
       <c r="L72" s="23" t="n">
         <v>0</v>
@@ -6471,25 +6468,25 @@
         <v>364</v>
       </c>
       <c r="E73" s="23" t="n">
-        <v>14989.09</v>
+        <v>27150</v>
       </c>
       <c r="F73" s="23" t="n">
-        <v>23.27</v>
+        <v>188.36</v>
       </c>
       <c r="G73" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="23" t="n">
-        <v>15012.36</v>
+        <v>27338.36</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>1501.24</v>
+        <v>2733.84</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>1501.24</v>
+        <v>1366.92</v>
       </c>
       <c r="K73" s="23" t="n">
-        <v>1501.24</v>
+        <v>1366.92</v>
       </c>
       <c r="L73" s="23" t="n">
         <v>0</v>
@@ -6509,25 +6506,25 @@
         <v>367</v>
       </c>
       <c r="E74" s="23" t="n">
-        <v>11750</v>
+        <v>22616.36</v>
       </c>
       <c r="F74" s="23" t="n">
-        <v>-40.23</v>
+        <v>-265.09</v>
       </c>
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="23" t="n">
-        <v>11709.77</v>
+        <v>22351.27</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>1170.98</v>
+        <v>2235.13</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>585.49</v>
+        <v>1117.56</v>
       </c>
       <c r="K74" s="23" t="n">
-        <v>585.49</v>
+        <v>1117.56</v>
       </c>
       <c r="L74" s="23" t="n">
         <v>0</v>
@@ -6544,28 +6541,28 @@
         <v>369</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E75" s="23" t="n">
-        <v>27150</v>
+        <v>26706.37</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>188.36</v>
+        <v>696.54</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="23" t="n">
-        <v>27338.36</v>
+        <v>27402.91</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>2733.84</v>
+        <v>240.29</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>1366.92</v>
+        <v>120.14</v>
       </c>
       <c r="K75" s="23" t="n">
-        <v>1366.92</v>
+        <v>120.14</v>
       </c>
       <c r="L75" s="23" t="n">
         <v>0</v>
@@ -6576,34 +6573,34 @@
         <v>203</v>
       </c>
       <c r="B76" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="D76" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="C76" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>373</v>
-      </c>
       <c r="E76" s="23" t="n">
-        <v>22616.36</v>
+        <v>17830</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>-265.09</v>
+        <v>-224.55</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="23" t="n">
-        <v>22351.27</v>
+        <v>17605.45</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>2235.13</v>
+        <v>1760.55</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>1117.56</v>
+        <v>880.27</v>
       </c>
       <c r="K76" s="23" t="n">
-        <v>1117.56</v>
+        <v>880.27</v>
       </c>
       <c r="L76" s="23" t="n">
         <v>0</v>
@@ -6614,34 +6611,34 @@
         <v>203</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E77" s="23" t="n">
-        <v>26706.37</v>
+        <v>29349.09</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>696.54</v>
+        <v>625.82</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>0</v>
+        <v>-4915.76</v>
       </c>
       <c r="H77" s="23" t="n">
-        <v>27402.91</v>
+        <v>25059.15</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>240.29</v>
+        <v>2505.92</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>120.14</v>
+        <v>715.98</v>
       </c>
       <c r="K77" s="23" t="n">
-        <v>120.14</v>
+        <v>715.98</v>
       </c>
       <c r="L77" s="23" t="n">
         <v>0</v>
@@ -6652,34 +6649,34 @@
         <v>203</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="C78" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="D78" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="D78" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="E78" s="23" t="n">
-        <v>17830</v>
+        <v>24280.9</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>-224.55</v>
+        <v>335.73</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="23" t="n">
-        <v>17605.45</v>
+        <v>24616.63</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>1760.55</v>
+        <v>2461.66</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>880.27</v>
+        <v>703.34</v>
       </c>
       <c r="K78" s="23" t="n">
-        <v>880.27</v>
+        <v>703.34</v>
       </c>
       <c r="L78" s="23" t="n">
         <v>0</v>
@@ -6690,34 +6687,34 @@
         <v>203</v>
       </c>
       <c r="B79" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="C79" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="D79" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="D79" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="E79" s="23" t="n">
-        <v>29349.09</v>
+        <v>24920.36</v>
       </c>
       <c r="F79" s="23" t="n">
-        <v>625.82</v>
+        <v>363.36</v>
       </c>
       <c r="G79" s="23" t="n">
-        <v>-4915.76</v>
+        <v>-5088.48</v>
       </c>
       <c r="H79" s="23" t="n">
-        <v>25059.15</v>
+        <v>20195.24</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>2505.92</v>
+        <v>2019.52</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>715.98</v>
+        <v>1009.76</v>
       </c>
       <c r="K79" s="23" t="n">
-        <v>715.98</v>
+        <v>1009.76</v>
       </c>
       <c r="L79" s="23" t="n">
         <v>0</v>
@@ -6737,25 +6734,25 @@
         <v>382</v>
       </c>
       <c r="E80" s="23" t="n">
-        <v>24280.9</v>
+        <v>25739.09</v>
       </c>
       <c r="F80" s="23" t="n">
-        <v>335.73</v>
+        <v>71.55</v>
       </c>
       <c r="G80" s="23" t="n">
-        <v>0</v>
+        <v>-3741</v>
       </c>
       <c r="H80" s="23" t="n">
-        <v>24616.63</v>
+        <v>22069.64</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>2461.66</v>
+        <v>2206.96</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>703.34</v>
+        <v>2206.96</v>
       </c>
       <c r="K80" s="23" t="n">
-        <v>703.34</v>
+        <v>2206.96</v>
       </c>
       <c r="L80" s="23" t="n">
         <v>0</v>
@@ -6775,155 +6772,123 @@
         <v>385</v>
       </c>
       <c r="E81" s="23" t="n">
-        <v>24920.36</v>
+        <v>26020.91</v>
       </c>
       <c r="F81" s="23" t="n">
-        <v>363.36</v>
+        <v>-93.64</v>
       </c>
       <c r="G81" s="23" t="n">
-        <v>-5088.48</v>
+        <v>-3960.3</v>
       </c>
       <c r="H81" s="23" t="n">
-        <v>20195.24</v>
+        <v>21966.97</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>2019.52</v>
+        <v>2196.7</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>1009.76</v>
+        <v>1647.51</v>
       </c>
       <c r="K81" s="23" t="n">
-        <v>1009.76</v>
+        <v>1647.51</v>
       </c>
       <c r="L81" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B82" s="22" t="s">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="7"/>
+      <c r="E82" s="8" t="n">
+        <f aca="false">SUM(E7:E81)</f>
+        <v>1748724.46</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <f aca="false">SUM(F7:F81)</f>
+        <v>-10023.87</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <f aca="false">SUM(G7:G81)</f>
+        <v>-110608.85</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <f aca="false">SUM(H7:H81)</f>
+        <v>1628091.74</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <f aca="false">SUM(I7:I81)</f>
+        <v>157452.59</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <f aca="false">SUM(J7:J81)</f>
+        <v>91820.52</v>
+      </c>
+      <c r="K82" s="8" t="n">
+        <f aca="false">SUM(K7:K81)</f>
+        <v>91820.52</v>
+      </c>
+      <c r="L82" s="8" t="n">
+        <f aca="false">SUM(L7:L81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="C82" s="21" t="s">
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="21"/>
+      <c r="B85" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="C85" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D85" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="E82" s="23" t="n">
-        <v>25739.09</v>
-      </c>
-      <c r="F82" s="23" t="n">
-        <v>71.55</v>
-      </c>
-      <c r="G82" s="23" t="n">
-        <v>-3741</v>
-      </c>
-      <c r="H82" s="23" t="n">
-        <v>22069.64</v>
-      </c>
-      <c r="I82" s="23" t="n">
-        <v>2206.96</v>
-      </c>
-      <c r="J82" s="23" t="n">
-        <v>2206.96</v>
-      </c>
-      <c r="K82" s="23" t="n">
-        <v>2206.96</v>
-      </c>
-      <c r="L82" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B83" s="22" t="s">
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
+      <c r="L85" s="21"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="21"/>
+      <c r="B86" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C86" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D86" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="E83" s="23" t="n">
-        <v>26020.91</v>
-      </c>
-      <c r="F83" s="23" t="n">
-        <v>-93.64</v>
-      </c>
-      <c r="G83" s="23" t="n">
-        <v>-3960.3</v>
-      </c>
-      <c r="H83" s="23" t="n">
-        <v>21966.97</v>
-      </c>
-      <c r="I83" s="23" t="n">
-        <v>2196.7</v>
-      </c>
-      <c r="J83" s="23" t="n">
-        <v>1647.51</v>
-      </c>
-      <c r="K83" s="23" t="n">
-        <v>1647.51</v>
-      </c>
-      <c r="L83" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D84" s="7"/>
-      <c r="E84" s="8" t="n">
-        <f aca="false">SUM(E7:E83)</f>
-        <v>1821586.28</v>
-      </c>
-      <c r="F84" s="8" t="n">
-        <f aca="false">SUM(F7:F83)</f>
-        <v>-8377.05</v>
-      </c>
-      <c r="G84" s="8" t="n">
-        <f aca="false">SUM(G7:G83)</f>
-        <v>-110608.85</v>
-      </c>
-      <c r="H84" s="8" t="n">
-        <f aca="false">SUM(H7:H83)</f>
-        <v>1702600.38</v>
-      </c>
-      <c r="I84" s="8" t="n">
-        <f aca="false">SUM(I7:I83)</f>
-        <v>164736.97</v>
-      </c>
-      <c r="J84" s="8" t="n">
-        <f aca="false">SUM(J7:J83)</f>
-        <v>95091.12</v>
-      </c>
-      <c r="K84" s="8" t="n">
-        <f aca="false">SUM(K7:K83)</f>
-        <v>95091.12</v>
-      </c>
-      <c r="L84" s="8" t="n">
-        <f aca="false">SUM(L7:L83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="24" t="s">
-        <v>392</v>
-      </c>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="21"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="21"/>
       <c r="B87" s="22" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="C87" s="21" t="s">
         <v>393</v>
@@ -6987,11 +6952,13 @@
       <c r="L89" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="E85:L85"/>
+    <mergeCell ref="E86:L86"/>
     <mergeCell ref="E87:L87"/>
     <mergeCell ref="E88:L88"/>
     <mergeCell ref="E89:L89"/>
@@ -7012,7 +6979,7 @@
     <tabColor rgb="FFF3ECD8"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -7117,761 +7084,781 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>395</v>
+        <v>200</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>201</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="D6" s="4" t="s">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>28085</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>14988</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>18157.5</v>
+      </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>311.14</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2553.18</v>
-      </c>
-      <c r="L6" s="6"/>
+        <v>1815.75</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>453.2</v>
+      </c>
       <c r="M6" s="6" t="n">
-        <v>2553.18</v>
+        <v>907.88</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>199</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="D7" s="4" t="s">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6"/>
+        <v>5447</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>6215.91</v>
+      </c>
       <c r="I7" s="6" t="n">
-        <v>0</v>
+        <v>144.09</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6"/>
+        <v>621.59</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>126.41</v>
+      </c>
       <c r="M7" s="6" t="n">
-        <v>0</v>
+        <v>621.6</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>12</v>
+        <v>412</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>19238</v>
-      </c>
-      <c r="H8" s="6"/>
+        <v>35355</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>26703.24</v>
+      </c>
       <c r="I8" s="6" t="n">
-        <v>0</v>
+        <v>-355.5</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>-5082.17</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1748.91</v>
-      </c>
-      <c r="L8" s="6"/>
+        <v>2670.32</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>-543.77</v>
+      </c>
       <c r="M8" s="6" t="n">
-        <v>1748.91</v>
-      </c>
-      <c r="N8" s="26" t="s">
-        <v>413</v>
+        <v>2670.3</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>37730</v>
-      </c>
-      <c r="H9" s="6"/>
+        <v>19737</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>18075.73</v>
+      </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>3430</v>
-      </c>
-      <c r="L9" s="6"/>
+        <v>1807.57</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>13.3</v>
+      </c>
       <c r="M9" s="6" t="n">
-        <v>3430</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>413</v>
+        <v>1807.56</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>12</v>
+        <v>414</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>14988</v>
+        <v>67927</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>18157.5</v>
+        <v>62379.46</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>311.14</v>
+        <v>627.64</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1815.75</v>
+        <v>6237.95</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>453.2</v>
+        <v>62.77</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>907.88</v>
-      </c>
-      <c r="N10" s="26" t="s">
-        <v>413</v>
+        <v>6237.99</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>12</v>
+        <v>415</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5447</v>
+        <v>19737</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6215.91</v>
+        <v>18104.55</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>144.09</v>
+        <v>161.82</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>621.59</v>
+        <v>1810.46</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>126.41</v>
+        <v>16.19</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>621.6</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>413</v>
+        <v>1810.45</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>35355</v>
+        <v>23763</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>26703.24</v>
+        <v>22046.66</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-355.5</v>
+        <v>613.45</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-5082.17</v>
+        <v>-4240.43</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>2670.32</v>
+        <v>2204.67</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-543.77</v>
+        <v>44.4</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>2670.3</v>
-      </c>
-      <c r="N12" s="26" t="s">
-        <v>413</v>
+        <v>2204.65</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>16</v>
+        <v>418</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>419</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>19737</v>
+        <v>7032</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>18075.73</v>
+        <v>6460.36</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>133</v>
+        <v>-416</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1807.57</v>
+        <v>646.04</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>13.3</v>
+        <v>6.77</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>1807.56</v>
-      </c>
-      <c r="N13" s="26" t="s">
-        <v>413</v>
+        <v>646.03</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>67927</v>
+        <v>28945</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>62379.46</v>
+        <v>26685.4</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>627.64</v>
+        <v>525.09</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>-4923.33</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>6237.95</v>
+        <v>2668.54</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>62.77</v>
+        <v>37.18</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>6237.99</v>
-      </c>
-      <c r="N14" s="26" t="s">
-        <v>413</v>
+        <v>2668.55</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>410</v>
       </c>
       <c r="O14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>186</v>
+        <v>383</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>187</v>
+        <v>384</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>162</v>
+        <v>385</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>418</v>
+        <v>40</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>19737</v>
+        <v>28992</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>18104.55</v>
+        <v>21966.97</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>161.82</v>
+        <v>-93.64</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0</v>
+        <v>-3960.3</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1810.46</v>
+        <v>2196.7</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>16.19</v>
+        <v>-438.94</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>1810.45</v>
+        <v>2196.68</v>
       </c>
       <c r="N15" s="26" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="O15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>188</v>
+        <v>380</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>189</v>
+        <v>381</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>162</v>
+        <v>382</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>420</v>
+        <v>15</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>23763</v>
+        <v>37273.2</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>22046.66</v>
+        <v>22069.64</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>613.45</v>
+        <v>71.55</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-4240.43</v>
+        <v>-3741</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2204.67</v>
+        <v>2206.96</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>44.4</v>
+        <v>-1181.51</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>2204.65</v>
+        <v>2206.96</v>
       </c>
       <c r="N16" s="26" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="O16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>183</v>
+        <v>378</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>163</v>
+        <v>379</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>421</v>
+        <v>16</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>20195.24</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-5088.48</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>2019.52</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>-625.93</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>2019.52</v>
+      </c>
+      <c r="N17" s="26" t="s">
         <v>422</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>7032</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>6460.36</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>-416</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>646.04</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>646.03</v>
-      </c>
-      <c r="N17" s="26" t="s">
-        <v>413</v>
       </c>
       <c r="O17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>184</v>
+        <v>374</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>185</v>
+        <v>375</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>163</v>
+        <v>376</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>28945</v>
+        <v>26747</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>26685.4</v>
+        <v>24616.63</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>525.09</v>
+        <v>335.73</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-4923.33</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>2668.54</v>
+        <v>2461.66</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>37.18</v>
+        <v>30.11</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>2668.55</v>
+        <v>2461.69</v>
       </c>
       <c r="N18" s="26" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="O18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>389</v>
+        <v>86</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>28992</v>
+        <v>17113</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>21966.97</v>
+        <v>17605.45</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-93.64</v>
+        <v>-224.55</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-3960.3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2196.7</v>
+        <v>1760.55</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-438.94</v>
+        <v>204.82</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>2196.68</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>411</v>
+        <v>1760.54</v>
+      </c>
+      <c r="N19" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>16</v>
+        <v>426</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>15</v>
+        <v>427</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>37273.2</v>
+        <v>27325</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>22069.64</v>
+        <v>25059.15</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>71.55</v>
+        <v>625.82</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-3741</v>
+        <v>-4915.76</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2206.96</v>
+        <v>2505.92</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-1181.51</v>
+        <v>21.83</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>2206.96</v>
-      </c>
-      <c r="N20" s="25" t="s">
-        <v>411</v>
+        <v>2505.93</v>
+      </c>
+      <c r="N20" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>16</v>
+        <v>428</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>29100</v>
+        <v>24878</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>20195.24</v>
+        <v>22351.27</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>363.36</v>
+        <v>-265.09</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-5088.48</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2019.52</v>
+        <v>2235.13</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-625.93</v>
+        <v>-26.51</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>2019.52</v>
-      </c>
-      <c r="N21" s="25" t="s">
-        <v>411</v>
+        <v>2235.12</v>
+      </c>
+      <c r="N21" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>29377</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>27402.91</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>696.54</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>240.29</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>-2430.35</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>240.28</v>
+      </c>
+      <c r="N22" s="26" t="s">
         <v>422</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>26747</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>24616.63</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>335.73</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>2461.66</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>2461.69</v>
-      </c>
-      <c r="N22" s="25" t="s">
-        <v>411</v>
       </c>
       <c r="O22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>86</v>
+        <v>362</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>12</v>
@@ -7880,223 +7867,223 @@
         <v>36</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>17113</v>
+        <v>23615</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>17605.45</v>
+        <v>27338.36</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-224.55</v>
+        <v>188.36</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1760.55</v>
+        <v>2733.84</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>204.82</v>
+        <v>587.02</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>1760.54</v>
-      </c>
-      <c r="N23" s="25" t="s">
-        <v>411</v>
+        <v>2733.84</v>
+      </c>
+      <c r="N23" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>429</v>
+        <v>15</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>27325</v>
+        <v>12925</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>25059.15</v>
+        <v>11709.77</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>625.82</v>
+        <v>-40.23</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-4915.76</v>
+        <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>2505.92</v>
+        <v>1170.98</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>21.83</v>
+        <v>-4.02</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>2505.93</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>411</v>
+        <v>1170.98</v>
+      </c>
+      <c r="N24" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>430</v>
+        <v>14</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>431</v>
+        <v>12</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>24878</v>
+        <v>16488</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>22351.27</v>
+        <v>15012.36</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-265.09</v>
+        <v>23.27</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2235.13</v>
+        <v>1501.24</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-26.51</v>
+        <v>2.33</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2235.12</v>
-      </c>
-      <c r="N25" s="25" t="s">
-        <v>411</v>
+        <v>1501.24</v>
+      </c>
+      <c r="N25" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>432</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>29377</v>
+        <v>15439</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>27402.91</v>
+        <v>18500.03</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>696.54</v>
+        <v>-19.27</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>240.29</v>
+        <v>1850</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-2430.35</v>
+        <v>446.45</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>240.28</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>411</v>
+        <v>1850.01</v>
+      </c>
+      <c r="N26" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>23615</v>
+        <v>78848</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>27338.36</v>
+        <v>55192.82</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>188.36</v>
+        <v>1616</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>-9847.73</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2733.84</v>
+        <v>5519.28</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>587.02</v>
+        <v>-1648.72</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>2733.84</v>
-      </c>
-      <c r="N27" s="25" t="s">
-        <v>411</v>
+        <v>5519.28</v>
+      </c>
+      <c r="N27" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>432</v>
+        <v>15</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>15</v>
@@ -8105,130 +8092,130 @@
         <v>36</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12925</v>
+        <v>45416.8</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>11709.77</v>
+        <v>38463.66</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-40.23</v>
+        <v>989.09</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>-6987.25</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1170.98</v>
+        <v>3846.37</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-4.02</v>
+        <v>-282.43</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1170.98</v>
-      </c>
-      <c r="N28" s="25" t="s">
-        <v>411</v>
+        <v>3846.37</v>
+      </c>
+      <c r="N28" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>14</v>
+        <v>431</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>12</v>
+        <v>431</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>16488</v>
+        <v>34986.6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>15012.36</v>
+        <v>30774</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>23.27</v>
+        <v>-1183.27</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1501.24</v>
+        <v>3077.4</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>2.33</v>
+        <v>-103.2</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>1501.24</v>
-      </c>
-      <c r="N29" s="25" t="s">
-        <v>411</v>
+        <v>3077.4</v>
+      </c>
+      <c r="N29" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>15439</v>
+        <v>26011.6</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>18500.03</v>
+        <v>21418.91</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-19.27</v>
+        <v>-49.27</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1850</v>
+        <v>2141.89</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>446.45</v>
+        <v>-222.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>1850.01</v>
-      </c>
-      <c r="N30" s="25" t="s">
-        <v>411</v>
+        <v>1070.94</v>
+      </c>
+      <c r="N30" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>15</v>
@@ -8240,43 +8227,43 @@
         <v>36</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>78848</v>
+        <v>35698.8</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>55192.82</v>
+        <v>25594.37</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1616</v>
+        <v>204.37</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-9847.73</v>
+        <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>5519.28</v>
+        <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-1648.72</v>
+        <v>-3245.35</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>5519.28</v>
-      </c>
-      <c r="N31" s="25" t="s">
-        <v>411</v>
+        <v>0</v>
+      </c>
+      <c r="N31" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>15</v>
+        <v>432</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>15</v>
@@ -8285,1123 +8272,1123 @@
         <v>36</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>45416.8</v>
+        <v>45915</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>38463.66</v>
+        <v>43140.09</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>989.09</v>
+        <v>1210.09</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-6987.25</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3846.37</v>
+        <v>4314.01</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-282.43</v>
+        <v>139.92</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>3846.37</v>
-      </c>
-      <c r="N32" s="25" t="s">
-        <v>411</v>
+        <v>4314.01</v>
+      </c>
+      <c r="N32" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>34986.6</v>
+        <v>20594.6</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>30774</v>
+        <v>15159.81</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-1183.27</v>
+        <v>-2419.64</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>-1920.55</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>3077.4</v>
+        <v>2200</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-103.2</v>
+        <v>327.76</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>3077.4</v>
-      </c>
-      <c r="N33" s="25" t="s">
-        <v>411</v>
+        <v>2200</v>
+      </c>
+      <c r="N33" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>15</v>
+        <v>433</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>26011.6</v>
+        <v>31267.25</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>21418.91</v>
+        <v>29040.7</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-49.27</v>
+        <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0</v>
+        <v>-5624.98</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2141.89</v>
+        <v>2904.07</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-222.8</v>
+        <v>61.59</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>1070.94</v>
-      </c>
-      <c r="N34" s="25" t="s">
-        <v>411</v>
+        <v>2904.05</v>
+      </c>
+      <c r="N34" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>15</v>
+        <v>434</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>15</v>
+        <v>415</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>35698.8</v>
+        <v>37882.25</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>25594.37</v>
+        <v>29963.05</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>204.37</v>
+        <v>922.36</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0</v>
+        <v>-5624.99</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0</v>
+        <v>2996.31</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>-3245.35</v>
+        <v>-447.53</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="25" t="s">
-        <v>411</v>
+        <v>2996.3</v>
+      </c>
+      <c r="N35" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>15</v>
+        <v>435</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>45915</v>
+        <v>22668</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>43140.09</v>
+        <v>17035.93</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1210.09</v>
+        <v>-1332.18</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0</v>
+        <v>-3148.25</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>4314.01</v>
+        <v>1703.59</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>139.92</v>
+        <v>-357.14</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>4314.01</v>
-      </c>
-      <c r="N36" s="25" t="s">
-        <v>411</v>
+        <v>1703.6</v>
+      </c>
+      <c r="N36" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>15</v>
+        <v>436</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>20594.6</v>
+        <v>35548</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>15159.81</v>
+        <v>27179.55</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-2419.64</v>
+        <v>-949.8</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-1920.55</v>
+        <v>-5225.2</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2200</v>
+        <v>2717.96</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>327.76</v>
+        <v>-513.68</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>2200</v>
-      </c>
-      <c r="N37" s="25" t="s">
-        <v>411</v>
+        <v>2717.95</v>
+      </c>
+      <c r="N37" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>31267.25</v>
+        <v>24667</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>29040.7</v>
+        <v>21951.09</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0</v>
+        <v>-138.91</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-5624.98</v>
+        <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>2904.07</v>
+        <v>2195.11</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>61.59</v>
+        <v>-47.34</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>2904.05</v>
-      </c>
-      <c r="N38" s="25" t="s">
-        <v>411</v>
+        <v>2195.1</v>
+      </c>
+      <c r="N38" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>37882.25</v>
+        <v>22630</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>29963.05</v>
+        <v>21195.27</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>922.36</v>
+        <v>1077.09</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-5624.99</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2996.31</v>
+        <v>2119.53</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-447.53</v>
+        <v>62.26</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>2996.3</v>
-      </c>
-      <c r="N39" s="25" t="s">
-        <v>411</v>
+        <v>2119.55</v>
+      </c>
+      <c r="N39" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>22668</v>
+        <v>36086</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>17035.93</v>
+        <v>31393.27</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-1332.18</v>
+        <v>566</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-3148.25</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1703.59</v>
+        <v>3139.33</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-357.14</v>
+        <v>-141.22</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>1703.6</v>
-      </c>
-      <c r="N40" s="25" t="s">
-        <v>411</v>
+        <v>3139.35</v>
+      </c>
+      <c r="N40" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>418</v>
+        <v>12</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>437</v>
+        <v>12</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>35548</v>
+        <v>33761.6</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>27179.55</v>
+        <v>27708.72</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-949.8</v>
+        <v>455.09</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-5225.2</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2717.96</v>
+        <v>2770.87</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-513.68</v>
+        <v>-298.37</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>2717.95</v>
-      </c>
-      <c r="N41" s="25" t="s">
-        <v>411</v>
+        <v>2770.87</v>
+      </c>
+      <c r="N41" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>24667</v>
+        <v>19261.6</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>21951.09</v>
+        <v>26809.55</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-138.91</v>
+        <v>1548.55</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>2195.11</v>
+        <v>2680.96</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>-47.34</v>
+        <v>929.91</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>2195.1</v>
-      </c>
-      <c r="N42" s="25" t="s">
-        <v>411</v>
+        <v>2680.98</v>
+      </c>
+      <c r="N42" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>22630</v>
+        <v>27025.4</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>21195.27</v>
+        <v>20744.36</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1077.09</v>
+        <v>-4801.09</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>2119.53</v>
+        <v>2074.44</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>62.26</v>
+        <v>-382.41</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>2119.55</v>
-      </c>
-      <c r="N43" s="25" t="s">
-        <v>411</v>
+        <v>2074.44</v>
+      </c>
+      <c r="N43" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>439</v>
+        <v>15</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>36086</v>
+        <v>26209.62</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>31393.27</v>
+        <v>23880</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>566</v>
+        <v>53.07</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3139.33</v>
+        <v>2388</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-141.22</v>
+        <v>5.31</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>3139.35</v>
-      </c>
-      <c r="N44" s="25" t="s">
-        <v>411</v>
+        <v>2388</v>
+      </c>
+      <c r="N44" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>33761.6</v>
+        <v>53448.08</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>27708.72</v>
+        <v>46590.14</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>455.09</v>
+        <v>-5689.37</v>
       </c>
       <c r="J45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>2770.87</v>
+        <v>4659.01</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-298.37</v>
+        <v>-199.91</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>2770.87</v>
-      </c>
-      <c r="N45" s="25" t="s">
-        <v>411</v>
+        <v>4659.01</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>19261.6</v>
+        <v>23526.6</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>26809.55</v>
+        <v>19873.48</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1548.55</v>
+        <v>993.64</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>-1528.34</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>2680.96</v>
+        <v>1987.35</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>929.91</v>
+        <v>-151.43</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>2680.98</v>
-      </c>
-      <c r="N46" s="25" t="s">
-        <v>411</v>
+        <v>1987.36</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>15</v>
+        <v>442</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>27025.4</v>
+        <v>29199.2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>20744.36</v>
+        <v>25934.73</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-4801.09</v>
+        <v>-610</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>2074.44</v>
+        <v>2593.47</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-382.41</v>
+        <v>-61</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>2074.44</v>
-      </c>
-      <c r="N47" s="25" t="s">
-        <v>411</v>
+        <v>2593.48</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>15</v>
+        <v>441</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>15</v>
+        <v>442</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>26209.62</v>
+        <v>38748.2</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>23880</v>
+        <v>30285.48</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>53.07</v>
+        <v>-3412.73</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-3506.34</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>2388</v>
+        <v>3028.55</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>5.31</v>
+        <v>-494.01</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>2388</v>
-      </c>
-      <c r="N48" s="25" t="s">
-        <v>411</v>
+        <v>3028.56</v>
+      </c>
+      <c r="N48" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>12</v>
+        <v>443</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>40</v>
+        <v>444</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>53448.08</v>
+        <v>24250</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>46590.14</v>
+        <v>20990.45</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-5689.37</v>
+        <v>-761.36</v>
       </c>
       <c r="J49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>4659.01</v>
+        <v>2099.05</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-199.91</v>
+        <v>-105.5</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>4659.01</v>
-      </c>
-      <c r="N49" s="25" t="s">
-        <v>411</v>
+        <v>2099.04</v>
+      </c>
+      <c r="N49" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>23526.6</v>
+        <v>32097.6</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>19873.48</v>
+        <v>30780.91</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>993.64</v>
+        <v>71.82</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-1528.34</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>1987.35</v>
+        <v>3078.09</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-151.43</v>
+        <v>160.13</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>1987.36</v>
-      </c>
-      <c r="N50" s="25" t="s">
-        <v>411</v>
+        <v>3078.08</v>
+      </c>
+      <c r="N50" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>29199.2</v>
+        <v>14851.2</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>25934.73</v>
+        <v>14424.91</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-610</v>
+        <v>1120.37</v>
       </c>
       <c r="J51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2593.47</v>
+        <v>1442.49</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-61</v>
+        <v>92.38</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>2593.48</v>
-      </c>
-      <c r="N51" s="25" t="s">
-        <v>411</v>
+        <v>1442.48</v>
+      </c>
+      <c r="N51" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>38748.2</v>
+        <v>31049.2</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>30285.48</v>
+        <v>27931.64</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-3412.73</v>
+        <v>-704.72</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-3506.34</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>3028.55</v>
+        <v>2793.16</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-494.01</v>
+        <v>-29.49</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>3028.56</v>
-      </c>
-      <c r="N52" s="25" t="s">
-        <v>411</v>
+        <v>1396.58</v>
+      </c>
+      <c r="N52" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>24250</v>
+        <v>48152.8</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>20990.45</v>
+        <v>36557.24</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-761.36</v>
+        <v>-375.09</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0</v>
+        <v>-6842.94</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>2099.05</v>
+        <v>3655.72</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-105.5</v>
+        <v>-721.81</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>2099.04</v>
-      </c>
-      <c r="N53" s="25" t="s">
-        <v>411</v>
+        <v>3655.74</v>
+      </c>
+      <c r="N53" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>32097.6</v>
+        <v>30114</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>30780.91</v>
+        <v>23598.95</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>71.82</v>
+        <v>-1460.73</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-3466.87</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>3078.09</v>
+        <v>2359.9</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>160.13</v>
+        <v>-377.74</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>3078.08</v>
-      </c>
-      <c r="N54" s="25" t="s">
-        <v>411</v>
+        <v>2359.92</v>
+      </c>
+      <c r="N54" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>14851.2</v>
+        <v>30394.4</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>14424.91</v>
+        <v>22983.38</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>1120.37</v>
+        <v>-3362.18</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-3790.81</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1442.49</v>
+        <v>2298.34</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>92.38</v>
+        <v>-464.79</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>1442.48</v>
-      </c>
-      <c r="N55" s="25" t="s">
-        <v>411</v>
+        <v>2298.36</v>
+      </c>
+      <c r="N55" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>15</v>
+        <v>440</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>71953.2</v>
+        <v>27098.8</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>66835</v>
+        <v>20725.29</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>1646.82</v>
+        <v>-899.82</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-2451.07</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>6541.2</v>
+        <v>2072.53</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0</v>
+        <v>-391</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>6541.2</v>
-      </c>
-      <c r="N56" s="25" t="s">
-        <v>411</v>
+        <v>2072.52</v>
+      </c>
+      <c r="N56" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>15</v>
@@ -9410,220 +9397,220 @@
         <v>36</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>31049.2</v>
+        <v>29890</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>27931.64</v>
+        <v>21320.77</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-704.72</v>
+        <v>2040.91</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-3496.51</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>2793.16</v>
+        <v>2132.08</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-29.49</v>
+        <v>-585.19</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>1396.58</v>
-      </c>
-      <c r="N57" s="25" t="s">
-        <v>411</v>
+        <v>2132.08</v>
+      </c>
+      <c r="N57" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>48152.8</v>
+        <v>16511.6</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>36557.24</v>
+        <v>15042.73</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-375.09</v>
+        <v>-5207.27</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-6842.94</v>
+        <v>0</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>3655.72</v>
+        <v>0</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-721.81</v>
+        <v>-1501.05</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>3655.74</v>
-      </c>
-      <c r="N58" s="25" t="s">
-        <v>411</v>
+        <v>0</v>
+      </c>
+      <c r="N58" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>30114</v>
+        <v>18139.6</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>23598.95</v>
+        <v>16631.82</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-1460.73</v>
+        <v>-636.36</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-3466.87</v>
+        <v>0</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>2359.9</v>
+        <v>1663.18</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-377.74</v>
+        <v>14.13</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>2359.92</v>
-      </c>
-      <c r="N59" s="25" t="s">
-        <v>411</v>
+        <v>1663.18</v>
+      </c>
+      <c r="N59" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>440</v>
+        <v>16</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>30394.4</v>
+        <v>19415.1</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>22983.38</v>
+        <v>17344.55</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-3362.18</v>
+        <v>-500</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-3790.81</v>
+        <v>0</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2298.34</v>
+        <v>1734.46</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-464.79</v>
+        <v>-30.55</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>2298.36</v>
-      </c>
-      <c r="N60" s="25" t="s">
-        <v>411</v>
+        <v>1734.46</v>
+      </c>
+      <c r="N60" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>440</v>
+        <v>15</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>27098.8</v>
+        <v>57409.2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>20725.29</v>
+        <v>44180.09</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-899.82</v>
+        <v>3168.36</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-2451.07</v>
+        <v>-9859.18</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2072.53</v>
+        <v>4418.01</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-391</v>
+        <v>-801.01</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>2072.52</v>
-      </c>
-      <c r="N61" s="25" t="s">
-        <v>411</v>
+        <v>4418.01</v>
+      </c>
+      <c r="N61" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>15</v>
@@ -9635,133 +9622,133 @@
         <v>36</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>29890</v>
+        <v>36436.2</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>21320.77</v>
+        <v>31313.45</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>2040.91</v>
+        <v>3526</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-3496.51</v>
+        <v>-5336.37</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>2132.08</v>
+        <v>3131.35</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-585.19</v>
+        <v>-181.03</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>2132.08</v>
-      </c>
-      <c r="N62" s="25" t="s">
-        <v>411</v>
+        <v>3131.35</v>
+      </c>
+      <c r="N62" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>446</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>16511.6</v>
+        <v>29420.2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>15042.73</v>
+        <v>27080.82</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>-5207.27</v>
+        <v>336.09</v>
       </c>
       <c r="J63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>0</v>
+        <v>2708.08</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>-1501.05</v>
+        <v>33.52</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="25" t="s">
-        <v>411</v>
+        <v>2708.07</v>
+      </c>
+      <c r="N63" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>18139.6</v>
+        <v>12877.6</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>16631.82</v>
+        <v>11878.18</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>-636.36</v>
+        <v>171.27</v>
       </c>
       <c r="J64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1663.18</v>
+        <v>1100</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>14.13</v>
+        <v>-70.69</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>1663.18</v>
-      </c>
-      <c r="N64" s="25" t="s">
-        <v>411</v>
+        <v>1100</v>
+      </c>
+      <c r="N64" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>16</v>
+        <v>431</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>15</v>
@@ -9770,40 +9757,40 @@
         <v>36</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>19415.1</v>
+        <v>21878</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>17344.55</v>
+        <v>20759.54</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>-500</v>
+        <v>1400.45</v>
       </c>
       <c r="J65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1734.46</v>
+        <v>2225</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>-30.55</v>
+        <v>236.09</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>1734.46</v>
-      </c>
-      <c r="N65" s="25" t="s">
-        <v>411</v>
+        <v>2225</v>
+      </c>
+      <c r="N65" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>15</v>
@@ -9815,43 +9802,43 @@
         <v>36</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>57409.2</v>
+        <v>15218</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>44180.09</v>
+        <v>13670.91</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>3168.36</v>
+        <v>-647.27</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>-9859.18</v>
+        <v>0</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>4418.01</v>
+        <v>1367.09</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>-801.01</v>
+        <v>-16.36</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>4418.01</v>
-      </c>
-      <c r="N66" s="25" t="s">
-        <v>411</v>
+        <v>1367.09</v>
+      </c>
+      <c r="N66" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>15</v>
@@ -9860,133 +9847,133 @@
         <v>36</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>36436.2</v>
+        <v>5000</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>31313.45</v>
+        <v>5250</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>3526</v>
+        <v>0</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>-5336.37</v>
+        <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>3131.35</v>
+        <v>1000</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>-181.03</v>
+        <v>545.45</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>3131.35</v>
-      </c>
-      <c r="N67" s="25" t="s">
-        <v>411</v>
+        <v>1000</v>
+      </c>
+      <c r="N67" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>29420.2</v>
+        <v>15535.6</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>27080.82</v>
+        <v>14478.36</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>336.09</v>
+        <v>355.09</v>
       </c>
       <c r="J68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>2708.08</v>
+        <v>1447.84</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>33.52</v>
+        <v>35.51</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>2708.07</v>
-      </c>
-      <c r="N68" s="25" t="s">
-        <v>411</v>
+        <v>1447.84</v>
+      </c>
+      <c r="N68" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>12877.6</v>
+        <v>22201</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>11878.18</v>
+        <v>20050.91</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>171.27</v>
+        <v>-122.73</v>
       </c>
       <c r="J69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>1100</v>
+        <v>2005.09</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>-70.69</v>
+        <v>-13.18</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N69" s="25" t="s">
-        <v>411</v>
+        <v>2005.08</v>
+      </c>
+      <c r="N69" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>15</v>
@@ -9995,40 +9982,40 @@
         <v>36</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>21878</v>
+        <v>13527.6</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>20759.54</v>
+        <v>12469.09</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>1400.45</v>
+        <v>171.27</v>
       </c>
       <c r="J70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2225</v>
+        <v>1246.91</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>236.09</v>
+        <v>17.13</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>2225</v>
-      </c>
-      <c r="N70" s="25" t="s">
-        <v>411</v>
+        <v>1246.91</v>
+      </c>
+      <c r="N70" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>15</v>
@@ -10040,100 +10027,100 @@
         <v>36</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>15218</v>
+        <v>10729</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>13670.91</v>
+        <v>9018.18</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>-647.27</v>
+        <v>-81.82</v>
       </c>
       <c r="J71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1367.09</v>
+        <v>901.82</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>-16.36</v>
+        <v>-73.54</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>1367.09</v>
-      </c>
-      <c r="N71" s="25" t="s">
-        <v>411</v>
+        <v>901.82</v>
+      </c>
+      <c r="N71" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>5000</v>
+        <v>17583</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>5250</v>
+        <v>15902.73</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>0</v>
+        <v>-81.82</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1000</v>
+        <v>1590.27</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>545.45</v>
+        <v>-8.18</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N72" s="25" t="s">
-        <v>411</v>
+        <v>1590.27</v>
+      </c>
+      <c r="N72" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>8175</v>
+        <v>5000</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>7673.64</v>
+        <v>2722.73</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>0</v>
@@ -10142,31 +10129,31 @@
         <v>0</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>743.18</v>
+        <v>272.27</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0</v>
+        <v>-182.28</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>743.18</v>
-      </c>
-      <c r="N73" s="25" t="s">
-        <v>411</v>
+        <v>272.27</v>
+      </c>
+      <c r="N73" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>15</v>
+        <v>445</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>15</v>
@@ -10175,85 +10162,85 @@
         <v>36</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>15535.6</v>
+        <v>4000</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>14478.36</v>
+        <v>3631.82</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>355.09</v>
+        <v>0</v>
       </c>
       <c r="J74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1447.84</v>
+        <v>350</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>35.51</v>
+        <v>-13.64</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>1447.84</v>
-      </c>
-      <c r="N74" s="25" t="s">
-        <v>411</v>
+        <v>350</v>
+      </c>
+      <c r="N74" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>22201</v>
+        <v>5250</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>20050.91</v>
+        <v>4699</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>-122.73</v>
+        <v>0</v>
       </c>
       <c r="J75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>2005.09</v>
+        <v>469.9</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>-13.18</v>
+        <v>-7.37</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>2005.08</v>
-      </c>
-      <c r="N75" s="25" t="s">
-        <v>411</v>
+        <v>469.9</v>
+      </c>
+      <c r="N75" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>15</v>
@@ -10265,40 +10252,40 @@
         <v>36</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>13527.6</v>
+        <v>10000</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>12469.09</v>
+        <v>9995</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>171.27</v>
+        <v>0</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>1246.91</v>
+        <v>999.5</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>17.13</v>
+        <v>90.41</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>1246.91</v>
-      </c>
-      <c r="N76" s="25" t="s">
-        <v>411</v>
+        <v>999.5</v>
+      </c>
+      <c r="N76" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>15</v>
@@ -10310,85 +10297,85 @@
         <v>36</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>10729</v>
+        <v>150</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>9018.18</v>
+        <v>136.36</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>-81.82</v>
+        <v>0</v>
       </c>
       <c r="J77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>901.82</v>
+        <v>13.64</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>-73.54</v>
+        <v>0</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>901.82</v>
-      </c>
-      <c r="N77" s="25" t="s">
-        <v>411</v>
+        <v>13.64</v>
+      </c>
+      <c r="N77" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>17583</v>
+        <v>20000</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>15902.73</v>
+        <v>17727.27</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>-81.82</v>
+        <v>0</v>
       </c>
       <c r="J78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1590.27</v>
+        <v>1772.73</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>-8.18</v>
+        <v>-45.45</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>1590.27</v>
-      </c>
-      <c r="N78" s="25" t="s">
-        <v>411</v>
+        <v>1772.73</v>
+      </c>
+      <c r="N78" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>15</v>
@@ -10420,23 +10407,23 @@
       <c r="M79" s="6" t="n">
         <v>272.27</v>
       </c>
-      <c r="N79" s="25" t="s">
-        <v>411</v>
+      <c r="N79" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>446</v>
+        <v>15</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>15</v>
@@ -10445,10 +10432,10 @@
         <v>36</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>3631.82</v>
+        <v>4086.36</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>0</v>
@@ -10457,329 +10444,59 @@
         <v>0</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>350</v>
+        <v>408.64</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>-13.64</v>
+        <v>-91.36</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>350</v>
-      </c>
-      <c r="N80" s="25" t="s">
-        <v>411</v>
+        <v>408.64</v>
+      </c>
+      <c r="N80" s="26" t="s">
+        <v>422</v>
       </c>
       <c r="O80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="6" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>4699</v>
-      </c>
-      <c r="I81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>469.9</v>
-      </c>
-      <c r="L81" s="6" t="n">
-        <v>-7.37</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>469.9</v>
-      </c>
-      <c r="N81" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O81" s="4"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G82" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H82" s="6" t="n">
-        <v>9995</v>
-      </c>
-      <c r="I82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="6" t="n">
-        <v>999.5</v>
-      </c>
-      <c r="L82" s="6" t="n">
-        <v>90.41</v>
-      </c>
-      <c r="M82" s="6" t="n">
-        <v>999.5</v>
-      </c>
-      <c r="N82" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O82" s="4"/>
+      <c r="A81" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="8" t="n">
+        <f aca="false">SUM(G6:G80)</f>
+        <v>1896283.1</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <f aca="false">SUM(H6:H80)</f>
+        <v>1628091.74</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <f aca="false">SUM(I6:I80)</f>
+        <v>-10023.87</v>
+      </c>
+      <c r="J81" s="8" t="n">
+        <f aca="false">SUM(J6:J80)</f>
+        <v>-110608.85</v>
+      </c>
+      <c r="K81" s="8" t="n">
+        <f aca="false">SUM(K6:K80)</f>
+        <v>157452.59</v>
+      </c>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8" t="n">
+        <f aca="false">SUM(M6:M80)</f>
+        <v>154077.23</v>
+      </c>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="H83" s="6" t="n">
-        <v>136.36</v>
-      </c>
-      <c r="I83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="L83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="6" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="N83" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O83" s="4"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G84" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H84" s="6" t="n">
-        <v>17727.27</v>
-      </c>
-      <c r="I84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="6" t="n">
-        <v>1772.73</v>
-      </c>
-      <c r="L84" s="6" t="n">
-        <v>-45.45</v>
-      </c>
-      <c r="M84" s="6" t="n">
-        <v>1772.73</v>
-      </c>
-      <c r="N84" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O84" s="4"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>2722.73</v>
-      </c>
-      <c r="I85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="6" t="n">
-        <v>272.27</v>
-      </c>
-      <c r="L85" s="6" t="n">
-        <v>-182.28</v>
-      </c>
-      <c r="M85" s="6" t="n">
-        <v>272.27</v>
-      </c>
-      <c r="N85" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O85" s="4"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H86" s="6" t="n">
-        <v>4086.36</v>
-      </c>
-      <c r="I86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="6" t="n">
-        <v>408.64</v>
-      </c>
-      <c r="L86" s="6" t="n">
-        <v>-91.36</v>
-      </c>
-      <c r="M86" s="6" t="n">
-        <v>408.64</v>
-      </c>
-      <c r="N86" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="O86" s="4"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="8" t="n">
-        <f aca="false">SUM(G6:G86)</f>
-        <v>2061464.3</v>
-      </c>
-      <c r="H87" s="8" t="n">
-        <f aca="false">SUM(H6:H86)</f>
-        <v>1702600.38</v>
-      </c>
-      <c r="I87" s="8" t="n">
-        <f aca="false">SUM(I6:I86)</f>
-        <v>-8377.05</v>
-      </c>
-      <c r="J87" s="8" t="n">
-        <f aca="false">SUM(J6:J86)</f>
-        <v>-110608.85</v>
-      </c>
-      <c r="K87" s="8" t="n">
-        <f aca="false">SUM(K6:K86)</f>
-        <v>172469.06</v>
-      </c>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8" t="n">
-        <f aca="false">SUM(M6:M86)</f>
-        <v>169093.7</v>
-      </c>
-      <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
-        <v>449</v>
+      <c r="A83" s="16" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -10813,35 +10530,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>452</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>454</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>21</v>
@@ -10852,7 +10569,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10860,7 +10577,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10868,7 +10585,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10876,7 +10593,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10884,28 +10601,28 @@
         <v>16</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="B12" s="28" t="s">
         <v>462</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="B13" s="28" t="s">
         <v>464</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>22</v>
@@ -10913,26 +10630,26 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="B15" s="28" t="s">
         <v>467</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B16" s="28" t="s">
         <v>469</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="B17" s="28" t="s">
         <v>471</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10940,7 +10657,7 @@
         <v>132</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -2159,14 +2159,14 @@
         <v>-4789.06</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3719.47</v>
       </c>
       <c r="F5" s="6" t="n">
         <f aca="false">C5+E5-D5</f>
-        <v>-6069.59</v>
+        <v>-8569.59</v>
       </c>
       <c r="G5" s="4" t="str">
         <f aca="false">IF(F5&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I5" s="6" t="n">
         <f aca="false">C5+E5+H5-D5</f>
-        <v>14510.46</v>
+        <v>12010.46</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">IF(I5&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2195,14 +2195,14 @@
         <v>-7730.41</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3715.38</v>
       </c>
       <c r="F6" s="6" t="n">
         <f aca="false">C6+E6-D6</f>
-        <v>-4015.03</v>
+        <v>-7265.03</v>
       </c>
       <c r="G6" s="4" t="str">
         <f aca="false">IF(F6&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I6" s="6" t="n">
         <f aca="false">C6+E6+H6-D6</f>
-        <v>8591.84</v>
+        <v>5341.84</v>
       </c>
       <c r="J6" s="4" t="str">
         <f aca="false">IF(I6&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>9706.25</v>
+        <v>15456.25</v>
       </c>
       <c r="E10" s="8" t="n">
         <f aca="false">SUM(E5:E9)</f>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">C10+E10-D10</f>
-        <v>-13193.98</v>
+        <v>-18943.98</v>
       </c>
       <c r="G10" s="7" t="str">
         <f aca="false">IF(F10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I10" s="8" t="n">
         <f aca="false">C10+E10+H10-D10</f>
-        <v>39406.01</v>
+        <v>33656.01</v>
       </c>
       <c r="J10" s="7" t="str">
         <f aca="false">IF(I10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -2267,14 +2267,14 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4706.25</v>
+        <v>4659.64</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>903.78</v>
       </c>
       <c r="F8" s="6" t="n">
         <f aca="false">C8+E8-D8</f>
-        <v>-3802.47</v>
+        <v>-3755.86</v>
       </c>
       <c r="G8" s="4" t="str">
         <f aca="false">IF(F8&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I8" s="6" t="n">
         <f aca="false">C8+E8+H8-D8</f>
-        <v>-1259.02</v>
+        <v>-1212.41</v>
       </c>
       <c r="J8" s="4" t="str">
         <f aca="false">IF(I8&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>15456.25</v>
+        <v>15409.64</v>
       </c>
       <c r="E10" s="8" t="n">
         <f aca="false">SUM(E5:E9)</f>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">C10+E10-D10</f>
-        <v>-18943.98</v>
+        <v>-18897.37</v>
       </c>
       <c r="G10" s="7" t="str">
         <f aca="false">IF(F10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I10" s="8" t="n">
         <f aca="false">C10+E10+H10-D10</f>
-        <v>33656.01</v>
+        <v>33702.62</v>
       </c>
       <c r="J10" s="7" t="str">
         <f aca="false">IF(I10&gt;=0,"AMPRA OWES","TO EARN BACK")</f>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="476">
   <si>
     <t xml:space="preserve">Ampra Commission Tracker — Team Position</t>
   </si>
@@ -1239,7 +1239,7 @@
     <t xml:space="preserve">75 deals · reference only, not counted in current positions · pull 28/08/26</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate up to 20/07/26. Figures before that date are reconstructed from HubSpot and contain known inconsistencies — 0 rows flagged below have no install date, no deal value, or no attribution recorded. Commission shown is earned/owed on install, not cash paid. Treat these totals as an estimate for cross-referencing, not a settled ledger.</t>
+    <t xml:space="preserve">Estimate up to 20/07/26. Figures before that date are reconstructed from HubSpot and contain known inconsistencies — 1 rows flagged below have no install date, no deal value, or no attribution recorded. Commission shown is earned/owed on install, not cash paid. Treat these totals as an estimate for cross-referencing, not a settled ledger.</t>
   </si>
   <si>
     <t xml:space="preserve">Formbay +/-</t>
@@ -1324,6 +1324,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing error - $2,500.00 deducted from Denzel</t>
   </si>
   <si>
     <t xml:space="preserve">Beau Jolly</t>
@@ -1665,7 +1668,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1787,6 +1790,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6581,10 +6592,10 @@
         <v>240.29</v>
       </c>
       <c r="J75" s="27" t="n">
-        <v>120.14</v>
+        <v>-1129.86</v>
       </c>
       <c r="K75" s="27" t="n">
-        <v>120.14</v>
+        <v>-1129.86</v>
       </c>
       <c r="L75" s="27" t="n">
         <v>0</v>
@@ -6847,11 +6858,11 @@
       </c>
       <c r="J82" s="8" t="n">
         <f aca="false">SUM(J7:J81)</f>
-        <v>91820.52</v>
+        <v>90570.52</v>
       </c>
       <c r="K82" s="8" t="n">
         <f aca="false">SUM(K7:K81)</f>
-        <v>91820.52</v>
+        <v>90570.52</v>
       </c>
       <c r="L82" s="8" t="n">
         <f aca="false">SUM(L7:L81)</f>
@@ -7825,49 +7836,51 @@
       <c r="O21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="31" t="n">
         <v>29377</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="31" t="n">
         <v>27402.91</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="31" t="n">
         <v>696.54</v>
       </c>
-      <c r="J22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
+      <c r="J22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="31" t="n">
         <v>240.29</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="31" t="n">
         <v>-2430.35</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="31" t="n">
         <v>240.28</v>
       </c>
-      <c r="N22" s="30" t="s">
+      <c r="N22" s="32" t="s">
         <v>424</v>
       </c>
-      <c r="O22" s="4"/>
+      <c r="O22" s="12" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
@@ -8150,10 +8163,10 @@
         <v>348</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>42</v>
@@ -8285,7 +8298,7 @@
         <v>339</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>15</v>
@@ -8330,7 +8343,7 @@
         <v>336</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>15</v>
@@ -8378,7 +8391,7 @@
         <v>417</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>48</v>
@@ -8420,7 +8433,7 @@
         <v>330</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>417</v>
@@ -8465,10 +8478,10 @@
         <v>330</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>48</v>
@@ -8513,7 +8526,7 @@
         <v>417</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>48</v>
@@ -8555,7 +8568,7 @@
         <v>322</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>417</v>
@@ -8648,7 +8661,7 @@
         <v>417</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>48</v>
@@ -8735,10 +8748,10 @@
         <v>309</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>48</v>
@@ -8780,7 +8793,7 @@
         <v>309</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>15</v>
@@ -8915,10 +8928,10 @@
         <v>301</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>48</v>
@@ -8960,10 +8973,10 @@
         <v>301</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>48</v>
@@ -9005,10 +9018,10 @@
         <v>296</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>48</v>
@@ -9050,10 +9063,10 @@
         <v>296</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>48</v>
@@ -9095,10 +9108,10 @@
         <v>291</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>48</v>
@@ -9140,10 +9153,10 @@
         <v>291</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>48</v>
@@ -9230,10 +9243,10 @@
         <v>285</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>48</v>
@@ -9275,10 +9288,10 @@
         <v>280</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>48</v>
@@ -9320,10 +9333,10 @@
         <v>280</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>48</v>
@@ -9365,10 +9378,10 @@
         <v>275</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>48</v>
@@ -9455,7 +9468,7 @@
         <v>272</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>20</v>
@@ -9500,10 +9513,10 @@
         <v>269</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>42</v>
@@ -9680,10 +9693,10 @@
         <v>257</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -9725,7 +9738,7 @@
         <v>254</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>15</v>
@@ -9770,7 +9783,7 @@
         <v>251</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>15</v>
@@ -9860,7 +9873,7 @@
         <v>245</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>15</v>
@@ -9950,10 +9963,10 @@
         <v>239</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>48</v>
@@ -10085,10 +10098,10 @@
         <v>231</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>48</v>
@@ -10175,7 +10188,7 @@
         <v>226</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>15</v>
@@ -10518,7 +10531,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -10552,134 +10565,134 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="33" t="s">
         <v>454</v>
       </c>
+      <c r="B4" s="34" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="33" t="s">
         <v>456</v>
       </c>
+      <c r="B5" s="34" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="B6" s="32" t="s">
+      <c r="A6" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6" s="34" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>458</v>
+      <c r="B7" s="34" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>459</v>
+      <c r="B8" s="34" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>460</v>
+      <c r="B9" s="34" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>461</v>
+      <c r="B10" s="34" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>462</v>
+      <c r="B11" s="34" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="B12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>464</v>
       </c>
+      <c r="B12" s="34" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="33" t="s">
         <v>466</v>
       </c>
+      <c r="B13" s="34" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
-        <v>467</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="A14" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>468</v>
-      </c>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="33" t="s">
         <v>469</v>
       </c>
+      <c r="B15" s="34" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
-        <v>470</v>
-      </c>
-      <c r="B16" s="32" t="s">
+      <c r="A16" s="33" t="s">
         <v>471</v>
       </c>
+      <c r="B16" s="34" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="s">
-        <v>472</v>
-      </c>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="33" t="s">
         <v>473</v>
       </c>
+      <c r="B17" s="34" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>474</v>
+      <c r="B18" s="34" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/Ampra_Commission_Tracker.xlsx
+++ b/Ampra_Commission_Tracker.xlsx
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="31" t="n">
-        <v>5956.36</v>
+        <v>6200.89</v>
       </c>
       <c r="E8" s="31" t="n">
         <v>903.78</v>
@@ -2505,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="24" min="1" max="2"/>
@@ -2874,7 +2874,7 @@
     <row r="23" ht="15" customHeight="1" s="25">
       <c r="A23" s="33" t="inlineStr">
         <is>
-          <t>21/08/26</t>
+          <t>23/08/26</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
@@ -2884,18 +2884,22 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>500</v>
-      </c>
-      <c r="E23" s="30" t="n"/>
+        <v>116.59</v>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
+        <is>
+          <t>gross $149.00 less $32.41 Ampra Job (recruitment)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="25">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>20/08/26</t>
+          <t>21/08/26</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
@@ -2905,22 +2909,18 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (AU)</t>
+          <t>Retainer</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="E24" s="30" t="inlineStr">
-        <is>
-          <t>gross $41.58 less $4.05 Ampra Job (recruitment)</t>
-        </is>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E24" s="30" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="25">
       <c r="A25" s="33" t="inlineStr">
         <is>
-          <t>20/08/26</t>
+          <t>21/08/26</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
@@ -2934,18 +2934,18 @@
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>129.64</v>
+        <v>127.94</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
-          <t>sub-threshold; billed 19/08 UTC = 20/08 AEST</t>
+          <t>gross $149.00 less $21.06 Ampra Job (recruitment)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="25">
       <c r="A26" s="33" t="inlineStr">
         <is>
-          <t>18/08/26</t>
+          <t>20/08/26</t>
         </is>
       </c>
       <c r="B26" s="30" t="inlineStr">
@@ -2959,14 +2959,18 @@
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>149</v>
-      </c>
-      <c r="E26" s="30" t="n"/>
+        <v>37.53</v>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>gross $41.58 less $4.05 Ampra Job (recruitment)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="25">
       <c r="A27" s="33" t="inlineStr">
         <is>
-          <t>17/08/26</t>
+          <t>20/08/26</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -2976,22 +2980,22 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (NZ)</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>252.03</v>
+        <v>129.64</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>NZ$302.56 at 0.8330 (rate locked at the date struck)</t>
+          <t>sub-threshold; billed 19/08 UTC = 20/08 AEST</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="25">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>16/08/26</t>
+          <t>18/08/26</t>
         </is>
       </c>
       <c r="B28" s="30" t="inlineStr">
@@ -3012,7 +3016,7 @@
     <row r="29" ht="15" customHeight="1" s="25">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>14/08/26</t>
+          <t>17/08/26</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
@@ -3022,18 +3026,22 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (AU)</t>
+          <t>Meta ad spend (NZ)</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>149</v>
-      </c>
-      <c r="E29" s="30" t="n"/>
+        <v>252.03</v>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>NZ$302.56 at 0.8330 (rate locked at the date struck)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="25">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>12/08/26</t>
+          <t>16/08/26</t>
         </is>
       </c>
       <c r="B30" s="30" t="inlineStr">
@@ -3054,7 +3062,7 @@
     <row r="31" ht="15" customHeight="1" s="25">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>10/08/26</t>
+          <t>14/08/26</t>
         </is>
       </c>
       <c r="B31" s="30" t="inlineStr">
@@ -3075,48 +3083,44 @@
     <row r="32" ht="15" customHeight="1" s="25">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>09/08/26</t>
+          <t>12/08/26</t>
         </is>
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>Denzel Winterbeard</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>2500</v>
+        <v>149</v>
       </c>
       <c r="E32" s="30" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="25">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>09/08/26</t>
+          <t>10/08/26</t>
         </is>
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E33" s="30" t="inlineStr">
-        <is>
-          <t>Final — ceased on moving to Sales Ops Manager</t>
-        </is>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E33" s="30" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="25">
       <c r="A34" s="33" t="inlineStr">
@@ -3126,28 +3130,28 @@
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Denzel Winterbeard</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (AU)</t>
+          <t>Retainer</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>149</v>
+        <v>2500</v>
       </c>
       <c r="E34" s="30" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="25">
       <c r="A35" s="33" t="inlineStr">
         <is>
-          <t>07/08/26</t>
+          <t>09/08/26</t>
         </is>
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -3156,14 +3160,18 @@
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>500</v>
-      </c>
-      <c r="E35" s="30" t="n"/>
+        <v>1250</v>
+      </c>
+      <c r="E35" s="30" t="inlineStr">
+        <is>
+          <t>Final — ceased on moving to Sales Ops Manager</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="25">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>07/08/26</t>
+          <t>09/08/26</t>
         </is>
       </c>
       <c r="B36" s="30" t="inlineStr">
@@ -3184,7 +3192,7 @@
     <row r="37" ht="15" customHeight="1" s="25">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>05/08/26</t>
+          <t>07/08/26</t>
         </is>
       </c>
       <c r="B37" s="30" t="inlineStr">
@@ -3194,18 +3202,18 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (AU)</t>
+          <t>Retainer</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="E37" s="30" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="25">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>03/08/26</t>
+          <t>07/08/26</t>
         </is>
       </c>
       <c r="B38" s="30" t="inlineStr">
@@ -3226,7 +3234,7 @@
     <row r="39" ht="15" customHeight="1" s="25">
       <c r="A39" s="33" t="inlineStr">
         <is>
-          <t>02/08/26</t>
+          <t>05/08/26</t>
         </is>
       </c>
       <c r="B39" s="30" t="inlineStr">
@@ -3247,7 +3255,7 @@
     <row r="40" ht="15" customHeight="1" s="25">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>01/08/26</t>
+          <t>03/08/26</t>
         </is>
       </c>
       <c r="B40" s="30" t="inlineStr">
@@ -3268,7 +3276,7 @@
     <row r="41" ht="15" customHeight="1" s="25">
       <c r="A41" s="33" t="inlineStr">
         <is>
-          <t>30/07/26</t>
+          <t>02/08/26</t>
         </is>
       </c>
       <c r="B41" s="30" t="inlineStr">
@@ -3289,7 +3297,7 @@
     <row r="42" ht="15" customHeight="1" s="25">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>29/07/26</t>
+          <t>01/08/26</t>
         </is>
       </c>
       <c r="B42" s="30" t="inlineStr">
@@ -3310,48 +3318,44 @@
     <row r="43" ht="15" customHeight="1" s="25">
       <c r="A43" s="33" t="inlineStr">
         <is>
-          <t>26/07/26</t>
+          <t>30/07/26</t>
         </is>
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>Denzel Winterbeard</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D43" s="31" t="n">
-        <v>2500</v>
+        <v>149</v>
       </c>
       <c r="E43" s="30" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="25">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>26/07/26</t>
+          <t>29/07/26</t>
         </is>
       </c>
       <c r="B44" s="30" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Meta ad spend (AU)</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E44" s="30" t="inlineStr">
-        <is>
-          <t>Two days unpaid leave</t>
-        </is>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E44" s="30" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="25">
       <c r="A45" s="33" t="inlineStr">
@@ -3361,28 +3365,28 @@
       </c>
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Denzel Winterbeard</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>Meta ad spend (AU)</t>
+          <t>Retainer</t>
         </is>
       </c>
       <c r="D45" s="31" t="n">
-        <v>149</v>
+        <v>2500</v>
       </c>
       <c r="E45" s="30" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="25">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>24/07/26</t>
+          <t>26/07/26</t>
         </is>
       </c>
       <c r="B46" s="30" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
@@ -3391,18 +3395,18 @@
         </is>
       </c>
       <c r="D46" s="31" t="n">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>First draw</t>
+          <t>Two days unpaid leave</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="25">
       <c r="A47" s="33" t="inlineStr">
         <is>
-          <t>24/07/26</t>
+          <t>26/07/26</t>
         </is>
       </c>
       <c r="B47" s="30" t="inlineStr">
@@ -3423,59 +3427,105 @@
     <row r="48" ht="15" customHeight="1" s="25">
       <c r="A48" s="33" t="inlineStr">
         <is>
+          <t>24/07/26</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="inlineStr">
+        <is>
+          <t>Holly</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="n">
+        <v>750</v>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>First draw</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="25">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>24/07/26</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>Holly</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>Meta ad spend (AU)</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="n">
+        <v>149</v>
+      </c>
+      <c r="E49" s="30" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="25">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
           <t>22/07/26</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>Holly</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>Meta ad spend (AU)</t>
         </is>
       </c>
-      <c r="D48" s="31" t="n">
+      <c r="D50" s="31" t="n">
         <v>149</v>
       </c>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>billing period 19/07–22/07 straddles the 20/07 baseline — included in full</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="25">
-      <c r="A49" s="34" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>TOTAL DRAWN</t>
         </is>
       </c>
-      <c r="B49" s="44" t="n"/>
-      <c r="C49" s="44" t="n"/>
-      <c r="D49" s="35">
-        <f>SUM(D13:D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="44" t="inlineStr">
+      <c r="B51" s="44" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="35">
+        <f>SUM(D13:D50)</f>
+        <v/>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
         <is>
           <t>Must equal the Dashboard 'Retainer + Ad Spend' total</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="25">
-      <c r="A50" s="34" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="B50" s="44" t="n"/>
-      <c r="C50" s="44" t="n"/>
-      <c r="D50" s="35">
-        <f>D49-'📊 Dashboard'!D10</f>
-        <v/>
-      </c>
-      <c r="E50" s="44" t="inlineStr">
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="35">
+        <f>D51-'📊 Dashboard'!D10</f>
+        <v/>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
         <is>
           <t>Zero means the two tabs agree</t>
         </is>
